--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK39"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45964.39583333334</v>
+        <v>45964.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45964.41666666666</v>
+        <v>45964.375</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45964.41666666666</v>
+        <v>45964.375</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45964.41666666666</v>
+        <v>45964.39583333334</v>
       </c>
     </row>
     <row r="10">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45964.4375</v>
+        <v>45964.41666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45964.45833333334</v>
+        <v>45964.41666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45964.45833333334</v>
+        <v>45964.41666666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45964.5</v>
+        <v>45964.4375</v>
       </c>
     </row>
     <row r="16">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45964.52083333334</v>
+        <v>45964.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45964.52083333334</v>
+        <v>45964.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45964.54166666666</v>
+        <v>45964.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45964.54166666666</v>
+        <v>45964.5</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,10 +3024,10 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45964.5625</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45964.57291666666</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,27 +3208,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.5625</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.57291666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="33">
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>5.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="35">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.64583333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45964.75</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="38">
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.83333333334</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,126 +5401,1416 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Netherlands Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PSV II</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Willem II</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>45964.66666666666</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AlbinoLeffe</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Inter II</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>45964.6875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Alcione</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pro Patria</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="n">
+        <v>45964.6875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Ospitaletto</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dolomiti Bellunesi</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
+        <v>45964.6875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Vis Pesaro</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Juventus II</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="n">
+        <v>45964.6875</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Cracovia Kraków</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Zagłębie Lubin</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3" t="n">
+        <v>45964.6875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>45964.70833333334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45964.83333333334</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L39" t="n">
+      <c r="L49" t="n">
         <v>1.73</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M49" t="n">
         <v>3.25</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N49" t="n">
         <v>4.6</v>
       </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="Z49" t="n">
         <v>1.61</v>
       </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="3" t="n">
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
         <v>45964.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45964.5</v>
+        <v>45964.45833333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="M19" t="n">
-        <v>2.85</v>
+        <v>3.86</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>5.08</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45964.5</v>
+        <v>45964.45833333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
         <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45964.52083333334</v>
+        <v>45964.5</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45964.52083333334</v>
+        <v>45964.5</v>
       </c>
     </row>
     <row r="22">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45964.54166666666</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45964.54166666666</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45964.5625</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45964.57291666666</v>
+        <v>45964.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.54166666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.55208333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.5625</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="N30" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,27 +4627,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.2</v>
+        <v>2.24</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>1.6</v>
+        <v>2.73</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,27 +4885,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45964.64583333334</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="38">
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="39">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.64583333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="M45" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="48">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45964.83333333334</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="49">
@@ -6691,126 +6691,900 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AlbinoLeffe</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Inter II</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>45964.6875</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Ospitaletto</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dolomiti Bellunesi</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3" t="n">
+        <v>45964.6875</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3" t="n">
+        <v>45964.70833333334</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" s="3" t="n">
+        <v>45964.83333333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="L55" t="n">
         <v>1.73</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M55" t="n">
         <v>3.25</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N55" t="n">
         <v>4.6</v>
       </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="Z55" t="n">
         <v>1.61</v>
       </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3" t="n">
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="3" t="n">
         <v>45964.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK55"/>
+  <dimension ref="A1:AK56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.86</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>5.08</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="N25" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.55</v>
+        <v>1.99</v>
       </c>
       <c r="M30" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="N30" t="n">
-        <v>2.56</v>
+        <v>3.17</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.33</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="39">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="M39" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45964.64583333334</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.64583333334</v>
       </c>
     </row>
     <row r="44">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.1</v>
+        <v>1.82</v>
       </c>
       <c r="M51" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
         <v>2.2</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="52">
@@ -7078,27 +7078,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N52" t="n">
-        <v>3.86</v>
+        <v>3.56</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="53">
@@ -7207,27 +7207,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="M53" t="n">
         <v>3.15</v>
       </c>
       <c r="N53" t="n">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="M54" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="N54" t="n">
-        <v>4.4</v>
+        <v>3.07</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45964.83333333334</v>
+        <v>45964.79166666666</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="M55" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N55" t="n">
-        <v>4.6</v>
+        <v>3.86</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7585,7 +7585,136 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45964.89583333334</v>
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="3" t="n">
+        <v>45964.83333333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK56"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3939,10 +3939,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="M30" t="n">
-        <v>3.31</v>
+        <v>3.47</v>
       </c>
       <c r="N30" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.57291666666</v>
       </c>
     </row>
     <row r="31">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.55</v>
+        <v>1.84</v>
       </c>
       <c r="M31" t="n">
-        <v>3.38</v>
+        <v>3.59</v>
       </c>
       <c r="N31" t="n">
-        <v>2.56</v>
+        <v>4.36</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>3.23</v>
       </c>
       <c r="N33" t="n">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4929,10 +4929,10 @@
         <v>2.15</v>
       </c>
       <c r="M35" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="M36" t="n">
-        <v>3.47</v>
+        <v>3.31</v>
       </c>
       <c r="N36" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.36</v>
+        <v>4.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.66</v>
+        <v>1.63</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>4.63</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,7 +5352,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
         <v>2</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,27 +5401,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N39" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,50 +5571,50 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="N40" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z40" t="n">
         <v>1.53</v>
       </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AA40" t="n">
         <v>0</v>
       </c>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="41">
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="M41" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="N41" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="M43" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45964.64583333334</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.64583333334</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="54">
@@ -7336,27 +7336,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="55">
@@ -7465,27 +7465,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="M55" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N55" t="n">
-        <v>3.86</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="56">
@@ -7594,127 +7594,901 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Vis Pesaro</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Juventus II</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" s="3" t="n">
+        <v>45964.6875</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N57" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" s="3" t="n">
+        <v>45964.69791666666</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N58" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3" t="n">
+        <v>45964.70833333334</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N59" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L56" t="n">
+      <c r="L61" t="n">
         <v>1.75</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M61" t="n">
         <v>3.55</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N61" t="n">
         <v>4.4</v>
       </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
         <v>2</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="Z61" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" s="3" t="n">
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3" t="n">
         <v>45964.83333333334</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3" t="n">
+        <v>45964.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AK64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N22" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.59</v>
+        <v>3.23</v>
       </c>
       <c r="N31" t="n">
-        <v>4.36</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="M33" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="M36" t="n">
-        <v>3.31</v>
+        <v>3.59</v>
       </c>
       <c r="N36" t="n">
-        <v>3.17</v>
+        <v>4.36</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.6</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>4.6</v>
+        <v>3.38</v>
       </c>
       <c r="N37" t="n">
-        <v>1.63</v>
+        <v>2.56</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.56</v>
+        <v>4.63</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="M40" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="N40" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="M41" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.6</v>
+        <v>2.62</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.56</v>
+        <v>1.82</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.62</v>
+        <v>4.6</v>
       </c>
       <c r="M47" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45964.69791666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="M58" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>2.45</v>
+        <v>5.8</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.69791666666</v>
       </c>
     </row>
     <row r="59">
@@ -7981,27 +7981,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="M59" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="N59" t="n">
-        <v>3.07</v>
+        <v>2.45</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="60">
@@ -8110,27 +8110,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.87</v>
+        <v>2.86</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="N60" t="n">
-        <v>3.86</v>
+        <v>2.6</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.75</v>
+        <v>2.26</v>
       </c>
       <c r="M61" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="N61" t="n">
-        <v>4.4</v>
+        <v>3.07</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45964.83333333334</v>
+        <v>45964.79166666666</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="M62" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N62" t="n">
-        <v>4.6</v>
+        <v>3.86</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8488,6 +8488,264 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3" t="n">
+        <v>45964.83333333334</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3" t="n">
         <v>45964.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.9</v>
+        <v>4.63</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="M34" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.17</v>
+        <v>3.42</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N37" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N39" t="n">
-        <v>4.63</v>
+        <v>2.56</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>4.6</v>
       </c>
       <c r="M45" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N46" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="M59" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="N59" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="M60" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="N60" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="M61" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>3.07</v>
+        <v>3.86</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="M62" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N62" t="n">
-        <v>3.86</v>
+        <v>3.07</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK64"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.86</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>5.08</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,16 +3411,16 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3939,10 +3939,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N31" t="n">
-        <v>4.63</v>
+        <v>4.36</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.63</v>
+        <v>3.42</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N34" t="n">
-        <v>3.42</v>
+        <v>3.17</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.99</v>
+        <v>4.6</v>
       </c>
       <c r="M38" t="n">
-        <v>3.31</v>
+        <v>4.6</v>
       </c>
       <c r="N38" t="n">
-        <v>3.17</v>
+        <v>1.63</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M39" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N39" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N41" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="M42" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="M45" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="M46" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="N46" t="n">
-        <v>3.3</v>
+        <v>2.28</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.69791666666</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N58" t="n">
-        <v>5.8</v>
+        <v>2.45</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45964.69791666666</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="M59" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="N59" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8055,16 +8055,16 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.73958333334</v>
       </c>
     </row>
     <row r="60">
@@ -8110,27 +8110,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="M60" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>2.45</v>
+        <v>3.86</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.79166666666</v>
       </c>
     </row>
     <row r="61">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N61" t="n">
-        <v>3.86</v>
+        <v>3.07</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="M62" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="N62" t="n">
-        <v>3.07</v>
+        <v>4.8</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,264 +8488,6 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45964.79166666666</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>45964</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Santos</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M63" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N63" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK63" s="3" t="n">
-        <v>45964.83333333334</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>45964</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Volta Redonda</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N64" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK64" s="3" t="n">
         <v>45964.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AK61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45964.375</v>
+        <v>45964.39583333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45964.39583333334</v>
+        <v>45964.41666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45964.41666666666</v>
+        <v>45964.4375</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45964.4375</v>
+        <v>45964.45833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45964.45833333334</v>
+        <v>45964.5</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45964.5</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="22">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3540,16 +3540,16 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,10 +3669,10 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45964.52083333334</v>
+        <v>45964.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45964.54166666666</v>
+        <v>45964.55208333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45964.55208333334</v>
+        <v>45964.5625</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.5625</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45964.57291666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>4.36</v>
+        <v>3.42</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="N32" t="n">
-        <v>4.63</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="N33" t="n">
-        <v>3.42</v>
+        <v>4.36</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.6</v>
+        <v>2.38</v>
       </c>
       <c r="M38" t="n">
-        <v>4.6</v>
+        <v>3.02</v>
       </c>
       <c r="N38" t="n">
-        <v>1.63</v>
+        <v>3.13</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,50 +5442,50 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z39" t="n">
         <v>2.15</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AA39" t="n">
         <v>0</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="M40" t="n">
-        <v>3.02</v>
+        <v>3.47</v>
       </c>
       <c r="N40" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.58</v>
+        <v>2.03</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45964.60416666666</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="41">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="M41" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.03</v>
+        <v>4.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="43">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.6</v>
+        <v>2.57</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>1.53</v>
+        <v>2.55</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.64583333334</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45964.64583333334</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="49">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="52">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="M54" t="n">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.69791666666</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N57" t="n">
-        <v>5.8</v>
+        <v>2.45</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45964.69791666666</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,49 +7893,49 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="M58" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="N58" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X58" t="n">
         <v>2.45</v>
       </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.73958333334</v>
       </c>
     </row>
     <row r="59">
@@ -7981,27 +7981,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,78 +8022,78 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="M59" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N59" t="n">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W59" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH59" t="n">
         <v>1.55</v>
       </c>
-      <c r="X59" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y59" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>0</v>
-      </c>
       <c r="AI59" t="n">
         <v>0</v>
       </c>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45964.73958333334</v>
+        <v>45964.75</v>
       </c>
     </row>
     <row r="60">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="M61" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="N61" t="n">
-        <v>3.07</v>
+        <v>4.8</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,135 +8359,6 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45964.79166666666</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>45964</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Volta Redonda</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Botafogo SP</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M62" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N62" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" s="3" t="n">
         <v>45964.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK61"/>
+  <dimension ref="A1:AK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45964.39583333334</v>
+        <v>45964.375</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45964.41666666666</v>
+        <v>45964.39583333334</v>
       </c>
     </row>
     <row r="10">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45964.41666666666</v>
+        <v>45964.4375</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45964.41666666666</v>
+        <v>45964.4375</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45964.4375</v>
+        <v>45964.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
         <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45964.45833333334</v>
+        <v>45964.5</v>
       </c>
     </row>
     <row r="19">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45964.5</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45964.52083333334</v>
+        <v>45964.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,55 +3765,55 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.7</v>
       </c>
-      <c r="M26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
       <c r="AA26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45964.54166666666</v>
+        <v>45964.55208333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45964.55208333334</v>
+        <v>45964.5625</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45964.5625</v>
+        <v>45964.57291666666</v>
       </c>
     </row>
     <row r="29">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="M32" t="n">
-        <v>3.23</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>4.36</v>
+        <v>3.42</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>3.17</v>
+        <v>4.63</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N36" t="n">
-        <v>4.63</v>
+        <v>2.56</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.6</v>
+        <v>1.84</v>
       </c>
       <c r="M37" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="N37" t="n">
-        <v>1.63</v>
+        <v>4.36</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="M40" t="n">
-        <v>3.47</v>
+        <v>3.36</v>
       </c>
       <c r="N40" t="n">
-        <v>3.19</v>
+        <v>2.66</v>
       </c>
       <c r="O40" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2.03</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2</v>
-      </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.6</v>
+        <v>2.62</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="M52" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N54" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="N56" t="n">
-        <v>5.8</v>
+        <v>3.56</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45964.69791666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="M57" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
-        <v>2.45</v>
+        <v>5.8</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.69791666666</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="M58" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N58" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7926,16 +7926,16 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45964.73958333334</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="59">
@@ -7981,27 +7981,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="M59" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N59" t="n">
-        <v>3.07</v>
+        <v>3.35</v>
       </c>
       <c r="O59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="X59" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45964.75</v>
+        <v>45964.73958333334</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N60" t="n">
-        <v>3.86</v>
+        <v>3.07</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.75</v>
       </c>
     </row>
     <row r="61">
@@ -8239,126 +8239,255 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N61" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L61" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M61" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N61" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
+      <c r="L62" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="Z62" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="3" t="n">
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3" t="n">
         <v>45964.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK62"/>
+  <dimension ref="A1:AK63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N21" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="X21" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="M29" t="n">
-        <v>3.23</v>
+        <v>3.47</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>3.19</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.57291666666</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4455,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.6</v>
+        <v>1.99</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.31</v>
       </c>
       <c r="N32" t="n">
-        <v>1.63</v>
+        <v>3.17</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4671,10 +4671,10 @@
         <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N33" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N34" t="n">
-        <v>4.63</v>
+        <v>4.36</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z34" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.56</v>
+        <v>4.63</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>4.36</v>
+        <v>3.42</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.60416666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="N39" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="M41" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z42" t="n">
         <v>1.75</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>1.53</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,55 +6345,55 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.6</v>
+        <v>1.86</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="N46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
         <v>1.53</v>
       </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
+      <c r="Z46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB46" t="n">
         <v>1.6</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="M59" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="N59" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W59" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X59" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45964.73958333334</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="60">
@@ -8110,27 +8110,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="M60" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N60" t="n">
-        <v>3.07</v>
+        <v>3.35</v>
       </c>
       <c r="O60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="X60" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AA60" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45964.75</v>
+        <v>45964.73958333334</v>
       </c>
     </row>
     <row r="61">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N61" t="n">
-        <v>3.86</v>
+        <v>3.07</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8368,126 +8368,255 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N62" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr">
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L62" t="n">
+      <c r="L63" t="n">
         <v>1.81</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M63" t="n">
         <v>3.17</v>
       </c>
-      <c r="N62" t="n">
+      <c r="N63" t="n">
         <v>3.96</v>
       </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z62" t="n">
+      <c r="Z63" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK62" s="3" t="n">
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3" t="n">
         <v>45964.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK63"/>
+  <dimension ref="A1:AK66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45964.4375</v>
+        <v>45964.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>2.97</v>
       </c>
       <c r="M16" t="n">
-        <v>3.86</v>
+        <v>3.09</v>
       </c>
       <c r="N16" t="n">
-        <v>5.08</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45964.45833333334</v>
+        <v>45964.5</v>
       </c>
     </row>
     <row r="18">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45964.5</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,10 +3024,10 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="N22" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45964.52083333334</v>
+        <v>45964.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>4.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>1.67</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45964.54166666666</v>
+        <v>45964.55208333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45964.55208333334</v>
+        <v>45964.5625</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.85</v>
+        <v>1.93</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45964.5625</v>
+        <v>45964.57291666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45964.57291666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.19</v>
+        <v>4.63</v>
       </c>
       <c r="O29" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.57291666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>1.99</v>
       </c>
       <c r="M31" t="n">
-        <v>4.6</v>
+        <v>3.31</v>
       </c>
       <c r="N31" t="n">
-        <v>1.63</v>
+        <v>3.17</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.99</v>
+        <v>4.6</v>
       </c>
       <c r="M32" t="n">
-        <v>3.31</v>
+        <v>4.6</v>
       </c>
       <c r="N32" t="n">
-        <v>3.17</v>
+        <v>1.63</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M35" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>3.42</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="N36" t="n">
-        <v>4.63</v>
+        <v>2.9</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Z36" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="N37" t="n">
-        <v>3.42</v>
+        <v>3.13</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="M39" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="N39" t="n">
-        <v>3.13</v>
+        <v>2.66</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.60416666666</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="41">
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.03</v>
+        <v>4.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="42">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N44" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
         <v>2.55</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45964.64583333334</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.64583333334</v>
       </c>
     </row>
     <row r="49">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="53">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45964.69791666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="M58" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7935,7 +7935,7 @@
         <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="59">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="M59" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="N59" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="O59" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P59" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R59" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="S59" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="T59" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W59" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X59" t="n">
         <v>3.4</v>
       </c>
-      <c r="U59" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V59" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W59" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X59" t="n">
-        <v>2.51</v>
-      </c>
       <c r="Y59" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AA59" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AC59" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD59" t="n">
         <v>2.05</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>1.73</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.69791666666</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="M60" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8184,16 +8184,16 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45964.73958333334</v>
+        <v>45964.69791666666</v>
       </c>
     </row>
     <row r="61">
@@ -8239,27 +8239,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="M61" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="N61" t="n">
-        <v>3.07</v>
+        <v>2.45</v>
       </c>
       <c r="O61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,27 +8368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.87</v>
+        <v>2.86</v>
       </c>
       <c r="M62" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O62" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q62" t="n">
         <v>3.3</v>
       </c>
-      <c r="N62" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,126 +8497,513 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X63" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3" t="n">
+        <v>45964.73958333334</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr">
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L63" t="n">
+      <c r="L66" t="n">
         <v>1.81</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M66" t="n">
         <v>3.17</v>
       </c>
-      <c r="N63" t="n">
+      <c r="N66" t="n">
         <v>3.96</v>
       </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z63" t="n">
+      <c r="Z66" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK63" s="3" t="n">
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" s="3" t="n">
         <v>45964.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK66"/>
+  <dimension ref="A1:AK69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45964.45833333334</v>
+        <v>45964.4375</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45964.5</v>
+        <v>45964.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45964.52083333334</v>
+        <v>45964.5</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,10 +3024,10 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45964.54166666666</v>
+        <v>45964.52083333334</v>
       </c>
     </row>
     <row r="24">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M25" t="n">
         <v>4.5</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.33</v>
-      </c>
       <c r="N25" t="n">
-        <v>1.67</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45964.55208333334</v>
+        <v>45964.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45964.5625</v>
+        <v>45964.55208333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.93</v>
+        <v>2.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45964.57291666666</v>
+        <v>45964.5625</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.57291666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N29" t="n">
-        <v>4.63</v>
+        <v>3.19</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.57291666666</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.56</v>
+        <v>3.42</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.17</v>
+        <v>4.63</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="N35" t="n">
-        <v>3.42</v>
+        <v>4.36</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="M36" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N36" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="N37" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45964.60416666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="M39" t="n">
-        <v>3.36</v>
+        <v>3.02</v>
       </c>
       <c r="N39" t="n">
-        <v>2.66</v>
+        <v>3.13</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.6</v>
+        <v>2.03</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="42">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.62</v>
+        <v>1.86</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="M44" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>3.3</v>
+        <v>2.28</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="M48" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
         <v>2.55</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45964.64583333334</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="49">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.64583333334</v>
       </c>
     </row>
     <row r="50">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45964.6875</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="55">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.81</v>
+        <v>1.96</v>
       </c>
       <c r="M59" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>2.26</v>
+        <v>3.9</v>
       </c>
       <c r="O59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45964.69791666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="60">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="M60" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O60" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA60" t="n">
         <v>4</v>
       </c>
-      <c r="N60" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45964.69791666666</v>
+        <v>45964.6875</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="M61" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="N61" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.69791666666</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.86</v>
+        <v>1.55</v>
       </c>
       <c r="M62" t="n">
-        <v>3.04</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>2.6</v>
+        <v>5.8</v>
       </c>
       <c r="O62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="AA62" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45964.70833333334</v>
+        <v>45964.69791666666</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="M63" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="N63" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W63" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X63" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45964.73958333334</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,27 +8626,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="65">
@@ -8755,27 +8755,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>3.07</v>
+        <v>2.45</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="AK65" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.70833333334</v>
       </c>
     </row>
     <row r="66">
@@ -8884,126 +8884,513 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M66" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X66" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" s="3" t="n">
+        <v>45964.73958333334</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X68" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG68" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3" t="n">
+        <v>45964.79166666666</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Volta Redonda</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Botafogo SP</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr">
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L66" t="n">
+      <c r="L69" t="n">
         <v>1.81</v>
       </c>
-      <c r="M66" t="n">
+      <c r="M69" t="n">
         <v>3.17</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N69" t="n">
         <v>3.96</v>
       </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z66" t="n">
+      <c r="Z69" t="n">
         <v>1.6</v>
       </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" s="3" t="n">
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3" t="n">
         <v>45964.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,10 +3024,10 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.57291666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="N31" t="n">
-        <v>4.63</v>
+        <v>1.63</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.6</v>
+        <v>1.99</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.31</v>
       </c>
       <c r="N32" t="n">
-        <v>1.63</v>
+        <v>3.17</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="M35" t="n">
-        <v>3.59</v>
+        <v>3.23</v>
       </c>
       <c r="N35" t="n">
-        <v>4.36</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>3.17</v>
+        <v>4.63</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="M38" t="n">
-        <v>3.38</v>
+        <v>3.02</v>
       </c>
       <c r="N38" t="n">
-        <v>2.56</v>
+        <v>3.13</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="M39" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="N39" t="n">
-        <v>3.13</v>
+        <v>2.66</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.60416666666</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="40">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="M40" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2.03</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2</v>
-      </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.86</v>
+        <v>4.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>3.13</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,14 +6603,14 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.55</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N48" t="n">
         <v>3.3</v>
       </c>
-      <c r="N48" t="n">
-        <v>2.55</v>
-      </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7668,10 +7668,10 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="M57" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N58" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N59" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="M60" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N60" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="O60" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
         <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AA60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.81</v>
+        <v>1.55</v>
       </c>
       <c r="M61" t="n">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>2.26</v>
+        <v>5.8</v>
       </c>
       <c r="O61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.55</v>
+        <v>2.81</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="N62" t="n">
-        <v>5.8</v>
+        <v>2.26</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="M63" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N23" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="N25" t="n">
-        <v>3.95</v>
+        <v>3.73</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.6</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>1.63</v>
+        <v>4.63</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N33" t="n">
-        <v>3.42</v>
+        <v>2.56</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>4.6</v>
       </c>
       <c r="M34" t="n">
-        <v>3.59</v>
+        <v>4.6</v>
       </c>
       <c r="N34" t="n">
-        <v>4.36</v>
+        <v>1.63</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="M35" t="n">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N36" t="n">
-        <v>4.63</v>
+        <v>4.36</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z36" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="N37" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z40" t="n">
         <v>2.03</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2</v>
-      </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="M41" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="N42" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.98</v>
+        <v>2.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>2.31</v>
+        <v>2.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="N44" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.13</v>
+        <v>4.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="M56" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="N56" t="n">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7668,16 +7668,16 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N57" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="M58" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N58" t="n">
-        <v>3.56</v>
+        <v>3.15</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="M59" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N59" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8055,16 +8055,16 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="M60" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N60" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.55</v>
+        <v>2.81</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="N61" t="n">
-        <v>5.8</v>
+        <v>2.26</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.81</v>
+        <v>1.55</v>
       </c>
       <c r="M62" t="n">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>2.26</v>
+        <v>5.8</v>
       </c>
       <c r="O62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M63" t="n">
         <v>3.25</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="M67" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N67" t="n">
-        <v>3.86</v>
+        <v>3.07</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="M68" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>3.07</v>
+        <v>3.86</v>
       </c>
       <c r="O68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4197,10 +4197,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="N30" t="n">
-        <v>3.42</v>
+        <v>3.17</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="N31" t="n">
-        <v>4.63</v>
+        <v>2.9</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.6</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1.63</v>
+        <v>4.63</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.31</v>
+        <v>3.38</v>
       </c>
       <c r="N35" t="n">
-        <v>3.17</v>
+        <v>2.56</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="M36" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>4.36</v>
+        <v>3.42</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="M39" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="N39" t="n">
-        <v>2.66</v>
+        <v>3.19</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="M40" t="n">
-        <v>3.47</v>
+        <v>3.36</v>
       </c>
       <c r="N40" t="n">
-        <v>3.19</v>
+        <v>2.66</v>
       </c>
       <c r="O40" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="M42" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="M44" t="n">
-        <v>3.21</v>
+        <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.6</v>
+        <v>2.95</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.95</v>
+        <v>1.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="N47" t="n">
-        <v>2.31</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>3.58</v>
+        <v>3.21</v>
       </c>
       <c r="N48" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="M55" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N55" t="n">
-        <v>4.33</v>
+        <v>3.15</v>
       </c>
       <c r="O55" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AA55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="M56" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N56" t="n">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7668,16 +7668,16 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="M57" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="M58" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N58" t="n">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="N59" t="n">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8055,16 +8055,16 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="M60" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N60" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N63" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.86</v>
+        <v>2.42</v>
       </c>
       <c r="M64" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N64" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O64" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="M65" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="N65" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.09</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
         <v>3.3</v>
@@ -2871,52 +2871,52 @@
         <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3000,34 +3000,34 @@
         <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y20" t="n">
         <v>2.05</v>
@@ -3036,16 +3036,16 @@
         <v>1.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N22" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="X22" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>3.73</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.9</v>
+        <v>3.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.28</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.83</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3774,34 +3774,34 @@
         <v>1.67</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y26" t="n">
         <v>2.17</v>
@@ -3810,16 +3810,16 @@
         <v>1.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3903,34 +3903,34 @@
         <v>2.35</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
         <v>1.8</v>
@@ -3939,16 +3939,16 @@
         <v>2</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.6</v>
+        <v>1.93</v>
       </c>
       <c r="M29" t="n">
-        <v>4.6</v>
+        <v>3.47</v>
       </c>
       <c r="N29" t="n">
-        <v>1.63</v>
+        <v>3.19</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.57291666666</v>
       </c>
     </row>
     <row r="30">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.99</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3.31</v>
+        <v>4.6</v>
       </c>
       <c r="N30" t="n">
-        <v>3.17</v>
+        <v>1.63</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.05</v>
+        <v>2.76</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4413,58 +4413,58 @@
         <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S31" t="n">
         <v>2.9</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.59</v>
+        <v>3.38</v>
       </c>
       <c r="N32" t="n">
-        <v>4.36</v>
+        <v>2.56</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>1.99</v>
       </c>
       <c r="M35" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="N35" t="n">
-        <v>2.56</v>
+        <v>3.17</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="M36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X36" t="n">
         <v>3.3</v>
       </c>
-      <c r="N36" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
       <c r="Y36" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="O38" t="n">
         <v>2.38</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.60416666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="M39" t="n">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="O39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y39" t="n">
         <v>2.52</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W39" t="n">
+      <c r="Z39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.18</v>
       </c>
-      <c r="X39" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="M40" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC40" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N41" t="n">
-        <v>3.1</v>
+        <v>2.66</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="N42" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N43" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N44" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z44" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="M45" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6606,58 +6606,58 @@
         <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6741,34 +6741,34 @@
         <v>2.55</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y49" t="n">
         <v>2.3</v>
@@ -6777,16 +6777,16 @@
         <v>1.63</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="M55" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N55" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7539,16 +7539,16 @@
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="M56" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N56" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7668,16 +7668,16 @@
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N57" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="M58" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N58" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="O58" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
         <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AA58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.7</v>
+        <v>1.82</v>
       </c>
       <c r="M60" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N60" t="n">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y60" t="n">
         <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.81</v>
+        <v>1.58</v>
       </c>
       <c r="M61" t="n">
-        <v>3.11</v>
+        <v>4.1</v>
       </c>
       <c r="N61" t="n">
-        <v>2.26</v>
+        <v>5.75</v>
       </c>
       <c r="O61" t="n">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="P61" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q61" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T61" t="n">
         <v>2.9</v>
       </c>
-      <c r="R61" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2.73</v>
-      </c>
       <c r="U61" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V61" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W61" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X61" t="n">
         <v>3.4</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.55</v>
+        <v>2.81</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="N62" t="n">
-        <v>5.8</v>
+        <v>2.26</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="M64" t="n">
         <v>3.25</v>
@@ -8676,52 +8676,52 @@
         <v>2.75</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>2.45</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -669,37 +669,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="O2" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.37</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
         <v>1.29</v>
@@ -708,22 +708,22 @@
         <v>3.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="P4" t="n">
         <v>2.01</v>
@@ -951,28 +951,28 @@
         <v>2.54</v>
       </c>
       <c r="T4" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
         <v>2.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.98</v>
+        <v>4.08</v>
       </c>
       <c r="AB4" t="n">
         <v>1.17</v>
@@ -997,7 +997,7 @@
         <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="P11" t="n">
         <v>1.83</v>
@@ -1863,10 +1863,10 @@
         <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
         <v>2.59</v>
@@ -1878,7 +1878,7 @@
         <v>5.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
         <v>2.18</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH11" t="n">
         <v>1.6</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.61</v>
+        <v>2.97</v>
       </c>
       <c r="M14" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O14" t="n">
         <v>3.5</v>
       </c>
-      <c r="N14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.15</v>
-      </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.35</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.12</v>
+        <v>3.48</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
         <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.91</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>4.85</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>2.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>5.46</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.59</v>
+        <v>3.07</v>
       </c>
       <c r="T16" t="n">
-        <v>3.09</v>
+        <v>2.7</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,31 +2604,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="M17" t="n">
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O17" t="n">
         <v>5.45</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
         <v>2.27</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
         <v>1.31</v>
@@ -2646,10 +2646,10 @@
         <v>2.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.78</v>
+        <v>4.03</v>
       </c>
       <c r="AB17" t="n">
         <v>1.19</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.11</v>
+        <v>2.68</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.14</v>
+        <v>4.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>2.33</v>
       </c>
       <c r="T20" t="n">
-        <v>2.39</v>
+        <v>3.68</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.6</v>
+        <v>5.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N21" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.69</v>
+        <v>3.14</v>
       </c>
       <c r="P21" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>3.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="T21" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="U21" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="X21" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.61</v>
+        <v>2.46</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.08</v>
+        <v>4.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
         <v>3.42</v>
@@ -3636,22 +3636,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="O25" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
         <v>1.17</v>
@@ -3663,7 +3663,7 @@
         <v>1.92</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
@@ -3672,25 +3672,25 @@
         <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC25" t="n">
         <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>1.67</v>
       </c>
       <c r="O26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P26" t="n">
         <v>2.18</v>
@@ -3786,16 +3786,16 @@
         <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="T26" t="n">
         <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
         <v>1.36</v>
@@ -3810,13 +3810,13 @@
         <v>1.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AB26" t="n">
         <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD26" t="n">
         <v>1.75</v>
@@ -3894,25 +3894,25 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="O27" t="n">
-        <v>3.85</v>
+        <v>3.77</v>
       </c>
       <c r="P27" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
         <v>2.96</v>
@@ -3927,10 +3927,10 @@
         <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
         <v>1.8</v>
@@ -3942,13 +3942,13 @@
         <v>2.79</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
         <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,49 +4152,49 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.47</v>
+        <v>3.23</v>
       </c>
       <c r="N29" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.91</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="U29" t="n">
         <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="AA29" t="n">
         <v>2.75</v>
@@ -4203,10 +4203,10 @@
         <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.57291666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>1.84</v>
       </c>
       <c r="M30" t="n">
-        <v>4.6</v>
+        <v>3.59</v>
       </c>
       <c r="N30" t="n">
-        <v>1.63</v>
+        <v>4.36</v>
       </c>
       <c r="O30" t="n">
-        <v>4.25</v>
+        <v>2.38</v>
       </c>
       <c r="P30" t="n">
-        <v>2.51</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>3.98</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
-        <v>1.88</v>
+        <v>2.93</v>
       </c>
       <c r="U30" t="n">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="V30" t="n">
         <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.97</v>
+        <v>3.41</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.69</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.2</v>
+        <v>2.02</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,34 +4410,34 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.42</v>
+        <v>4.63</v>
       </c>
       <c r="O31" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="T31" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V31" t="n">
         <v>1.05</v>
@@ -4446,25 +4446,25 @@
         <v>1.28</v>
       </c>
       <c r="X31" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>1.99</v>
       </c>
       <c r="M32" t="n">
-        <v>3.38</v>
+        <v>3.31</v>
       </c>
       <c r="N32" t="n">
-        <v>2.56</v>
+        <v>3.17</v>
       </c>
       <c r="O32" t="n">
-        <v>3.16</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="R32" t="n">
         <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="U32" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X32" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>4.63</v>
+        <v>3.05</v>
       </c>
       <c r="O33" t="n">
-        <v>2.25</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="T33" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="U33" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X33" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.99</v>
+        <v>3.94</v>
       </c>
       <c r="M35" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>3.17</v>
+        <v>1.62</v>
       </c>
       <c r="O35" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="P35" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.86</v>
+        <v>2.15</v>
       </c>
       <c r="R35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.33</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y35" t="n">
+      <c r="Z35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.78</v>
       </c>
-      <c r="Z35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC35" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,62 +5055,62 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>2.65</v>
+        <v>3.42</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="P36" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.33</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="T36" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U36" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="X36" t="n">
         <v>3.3</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD36" t="n">
         <v>2</v>
       </c>
-      <c r="Z36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="M37" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O37" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="U37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.5</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="M38" t="n">
-        <v>3.59</v>
+        <v>3.02</v>
       </c>
       <c r="N38" t="n">
-        <v>4.36</v>
+        <v>3.13</v>
       </c>
       <c r="O38" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.81</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.93</v>
+        <v>3.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W38" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="X38" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="Y38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD38" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
         <v>3.1</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="P39" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="T39" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="V39" t="n">
         <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="X39" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.55</v>
+        <v>2.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.60416666666</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="40">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,55 +5571,55 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="N40" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="O40" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="T40" t="n">
         <v>2.44</v>
       </c>
-      <c r="P40" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.56</v>
-      </c>
       <c r="U40" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
         <v>1.22</v>
       </c>
       <c r="X40" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC40" t="n">
         <v>1.62</v>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5712,16 +5712,16 @@
         <v>2.95</v>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="R41" t="n">
         <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
         <v>2.29</v>
@@ -5733,10 +5733,10 @@
         <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y41" t="n">
         <v>1.62</v>
@@ -5748,10 +5748,10 @@
         <v>2.51</v>
       </c>
       <c r="AB41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC41" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.53</v>
       </c>
       <c r="AD41" t="n">
         <v>2.45</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH41" t="n">
         <v>1.53</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.21</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="O42" t="n">
-        <v>3.69</v>
+        <v>4.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="R42" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="S42" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="T42" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="U42" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>3.08</v>
+        <v>4.75</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.86</v>
+        <v>2.85</v>
       </c>
       <c r="M43" t="n">
-        <v>3.58</v>
+        <v>3.21</v>
       </c>
       <c r="N43" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="O43" t="n">
-        <v>2.4</v>
+        <v>3.69</v>
       </c>
       <c r="P43" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="R43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.25</v>
       </c>
-      <c r="S43" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X43" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AC43" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6225,34 +6225,34 @@
         <v>2.28</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y45" t="n">
         <v>1.75</v>
@@ -6261,16 +6261,16 @@
         <v>2.1</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="O47" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="P47" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.44</v>
+        <v>2.72</v>
       </c>
       <c r="R47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U47" t="n">
         <v>1.35</v>
       </c>
-      <c r="S47" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="X47" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.92</v>
+        <v>3.75</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD47" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.85</v>
+        <v>1.86</v>
       </c>
       <c r="M48" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N48" t="n">
         <v>3.3</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X48" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA48" t="n">
         <v>2.35</v>
       </c>
-      <c r="O48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.78</v>
-      </c>
       <c r="AB48" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="M49" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O49" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P49" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="R49" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="S49" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="T49" t="n">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="U49" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V49" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W49" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="X49" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45964.64583333334</v>
+        <v>45964.625</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45964.66666666666</v>
+        <v>45964.64583333334</v>
       </c>
     </row>
     <row r="51">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="M55" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N55" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X55" t="n">
         <v>3.05</v>
       </c>
-      <c r="N55" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X55" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,43 +7635,43 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="M56" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y56" t="n">
         <v>2.2</v>
@@ -7680,16 +7680,16 @@
         <v>1.6</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="M57" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N57" t="n">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="M58" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N58" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="M59" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N59" t="n">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="M60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N60" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O60" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q60" t="n">
         <v>3.45</v>
       </c>
-      <c r="N60" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O60" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P60" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>4.96</v>
-      </c>
       <c r="R60" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S60" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="T60" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="U60" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V60" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W60" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X60" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y60" t="n">
         <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AA60" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>1.3</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,77 +8280,77 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.58</v>
+        <v>2.81</v>
       </c>
       <c r="M61" t="n">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="N61" t="n">
-        <v>5.75</v>
+        <v>2.26</v>
       </c>
       <c r="O61" t="n">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="P61" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="R61" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X61" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH61" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S61" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V61" t="n">
-        <v>1</v>
-      </c>
-      <c r="W61" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X61" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG61" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>2.3</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.81</v>
+        <v>1.55</v>
       </c>
       <c r="M62" t="n">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>2.26</v>
+        <v>5.8</v>
       </c>
       <c r="O62" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="P62" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="R62" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S62" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="T62" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U62" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V62" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W62" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X62" t="n">
         <v>3.4</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AB62" t="n">
         <v>1.3</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8547,34 +8547,34 @@
         <v>2.45</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y63" t="n">
         <v>2.2</v>
@@ -8583,16 +8583,16 @@
         <v>1.65</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,62 +8667,62 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.4</v>
+        <v>3.02</v>
       </c>
       <c r="M64" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O64" t="n">
-        <v>3.06</v>
+        <v>3.82</v>
       </c>
       <c r="P64" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.61</v>
+        <v>3.07</v>
       </c>
       <c r="R64" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S64" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="T64" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U64" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V64" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W64" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="X64" t="n">
-        <v>3.15</v>
+        <v>2.57</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AC64" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD64" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD64" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE64" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,77 +8796,77 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O65" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA65" t="n">
         <v>3.5</v>
       </c>
-      <c r="P65" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="AB65" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH65" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8934,28 +8934,28 @@
         <v>3.35</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W66" t="n">
         <v>1.55</v>
@@ -8970,16 +8970,16 @@
         <v>1.49</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9063,22 +9063,22 @@
         <v>3.07</v>
       </c>
       <c r="O67" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q67" t="n">
         <v>3.7</v>
       </c>
       <c r="R67" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S67" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="T67" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="U67" t="n">
         <v>1.27</v>
@@ -9087,10 +9087,10 @@
         <v>1.1</v>
       </c>
       <c r="W67" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="X67" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="Y67" t="n">
         <v>2.35</v>
@@ -9099,7 +9099,7 @@
         <v>1.53</v>
       </c>
       <c r="AA67" t="n">
-        <v>4.2</v>
+        <v>4.64</v>
       </c>
       <c r="AB67" t="n">
         <v>1.17</v>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45964.79166666666</v>
+        <v>45964.75</v>
       </c>
     </row>
     <row r="68">
@@ -9321,34 +9321,34 @@
         <v>3.96</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y69" t="n">
         <v>2.2</v>
@@ -9357,16 +9357,16 @@
         <v>1.6</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -675,22 +675,22 @@
         <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
         <v>2.76</v>
@@ -702,7 +702,7 @@
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X2" t="n">
         <v>3.4</v>
@@ -720,10 +720,10 @@
         <v>1.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.97</v>
+        <v>4.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.09</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>5.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.35</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.48</v>
+        <v>4.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M16" t="n">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
         <v>4.85</v>
       </c>
       <c r="O16" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.46</v>
+        <v>4.63</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.07</v>
+        <v>3.16</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U16" t="n">
         <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
         <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC16" t="n">
         <v>1.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="O23" t="n">
-        <v>2.08</v>
+        <v>2.68</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.21</v>
+        <v>4.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>2.33</v>
       </c>
       <c r="T23" t="n">
-        <v>2.43</v>
+        <v>3.68</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.6</v>
+        <v>5.06</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="M24" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.42</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>2.82</v>
+        <v>4.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.74</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>3.42</v>
+        <v>7</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.08</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="P25" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>4.42</v>
       </c>
       <c r="R25" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>4.25</v>
+        <v>2.82</v>
       </c>
       <c r="T25" t="n">
-        <v>1.92</v>
+        <v>2.74</v>
       </c>
       <c r="U25" t="n">
-        <v>1.88</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
-        <v>7</v>
+        <v>3.42</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.83</v>
+        <v>3.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="M29" t="n">
-        <v>3.23</v>
+        <v>3.47</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>3.19</v>
       </c>
       <c r="O29" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="T29" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
         <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
         <v>3.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.57291666666</v>
       </c>
     </row>
     <row r="30">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.84</v>
+        <v>3.94</v>
       </c>
       <c r="M30" t="n">
-        <v>3.59</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>4.36</v>
+        <v>1.62</v>
       </c>
       <c r="O30" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="P30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.93</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.41</v>
+        <v>1.92</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.26</v>
+        <v>1.78</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.02</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>4.63</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="T31" t="n">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="U31" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="Y31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,62 +4539,62 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="M32" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="T32" t="n">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="U32" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="X32" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="Z32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD32" t="n">
         <v>2.05</v>
       </c>
-      <c r="AA32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,19 +4668,19 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N33" t="n">
         <v>3.25</v>
       </c>
-      <c r="N33" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O33" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
         <v>3.6</v>
@@ -4689,40 +4689,40 @@
         <v>1.37</v>
       </c>
       <c r="S33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.77</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.72</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W33" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X33" t="n">
         <v>3.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="Z33" t="n">
         <v>1.83</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>4.58</v>
       </c>
       <c r="O34" t="n">
-        <v>3.16</v>
+        <v>2.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="R34" t="n">
         <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U34" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W34" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X34" t="n">
-        <v>4.15</v>
+        <v>3.62</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH34" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.94</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.62</v>
       </c>
-      <c r="O35" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AD35" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P36" t="n">
         <v>2.15</v>
       </c>
-      <c r="M36" t="n">
+      <c r="Q36" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
         <v>3.3</v>
       </c>
-      <c r="N36" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.36</v>
       </c>
-      <c r="S36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC36" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AD36" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>1.29</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5205,37 +5205,37 @@
         <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T37" t="n">
         <v>2.96</v>
       </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
         <v>1.31</v>
       </c>
       <c r="X37" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AA37" t="n">
         <v>3.28</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
         <v>1.95</v>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
         <v>1.5</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>3.02</v>
+        <v>3.23</v>
       </c>
       <c r="N38" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P38" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="T38" t="n">
-        <v>3.54</v>
+        <v>2.51</v>
       </c>
       <c r="U38" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="V38" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="X38" t="n">
-        <v>2.59</v>
+        <v>3.9</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.55</v>
+        <v>2.75</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.60416666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="N39" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O39" t="n">
         <v>3.1</v>
       </c>
-      <c r="O39" t="n">
-        <v>2.63</v>
-      </c>
       <c r="P39" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S39" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.67</v>
+        <v>3.54</v>
       </c>
       <c r="U39" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W39" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="X39" t="n">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.83</v>
+        <v>4.55</v>
       </c>
       <c r="AB39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.61458333334</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="40">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,55 +5571,55 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="M40" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S40" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="T40" t="n">
-        <v>2.44</v>
+        <v>2.67</v>
       </c>
       <c r="U40" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
         <v>1.22</v>
       </c>
       <c r="X40" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
         <v>1.62</v>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="O42" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.14</v>
+        <v>3.21</v>
       </c>
       <c r="R42" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="S42" t="n">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="T42" t="n">
-        <v>2.31</v>
+        <v>3.16</v>
       </c>
       <c r="U42" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W42" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="X42" t="n">
-        <v>4.75</v>
+        <v>2.83</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.5</v>
+        <v>3.84</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="M43" t="n">
-        <v>3.21</v>
+        <v>3.6</v>
       </c>
       <c r="N43" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="O43" t="n">
-        <v>3.69</v>
+        <v>4.2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="R43" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S43" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="T43" t="n">
-        <v>2.82</v>
+        <v>3.07</v>
       </c>
       <c r="U43" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="X43" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.62</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S45" t="n">
         <v>3.34</v>
       </c>
-      <c r="N45" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.15</v>
-      </c>
       <c r="T45" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="V45" t="n">
         <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X45" t="n">
-        <v>3.9</v>
+        <v>4.96</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,77 +6345,77 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="O46" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.21</v>
+        <v>2.14</v>
       </c>
       <c r="R46" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="S46" t="n">
-        <v>2.65</v>
+        <v>3.34</v>
       </c>
       <c r="T46" t="n">
-        <v>3.16</v>
+        <v>2.31</v>
       </c>
       <c r="U46" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="V46" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W46" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="X46" t="n">
-        <v>2.83</v>
+        <v>4.75</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.84</v>
+        <v>2.5</v>
       </c>
       <c r="AB46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC46" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH46" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,77 +6474,77 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>3.21</v>
       </c>
       <c r="N47" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="P47" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="R47" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S47" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="T47" t="n">
-        <v>3.07</v>
+        <v>2.82</v>
       </c>
       <c r="U47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH47" t="n">
         <v>1.35</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X47" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.33</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="M48" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="N48" t="n">
-        <v>3.3</v>
+        <v>2.28</v>
       </c>
       <c r="O48" t="n">
-        <v>2.19</v>
+        <v>3.25</v>
       </c>
       <c r="P48" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="R48" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S48" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="T48" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="U48" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="V48" t="n">
         <v>1.04</v>
       </c>
       <c r="W48" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X48" t="n">
-        <v>4.96</v>
+        <v>3.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="M49" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O49" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="P49" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.56</v>
+        <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="S49" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="T49" t="n">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="U49" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="V49" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W49" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="X49" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AD49" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45964.625</v>
+        <v>45964.64583333334</v>
       </c>
     </row>
     <row r="50">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45964.64583333334</v>
+        <v>45964.66666666666</v>
       </c>
     </row>
     <row r="51">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="M51" t="n">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="N51" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="O51" t="n">
         <v>2.75</v>
@@ -7005,37 +7005,37 @@
         <v>2.45</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R51" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S51" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="T51" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="U51" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V51" t="n">
         <v>1.03</v>
       </c>
       <c r="W51" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X51" t="n">
         <v>4.8</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AB51" t="n">
         <v>1.53</v>
@@ -7044,7 +7044,7 @@
         <v>1.44</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH51" t="n">
         <v>1.57</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N56" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="O56" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="P56" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.51</v>
+        <v>3.9</v>
       </c>
       <c r="R56" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S56" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="T56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X56" t="n">
         <v>3.2</v>
       </c>
-      <c r="U56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.85</v>
-      </c>
       <c r="Y56" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AA56" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AB56" t="n">
         <v>1.25</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="M57" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="O57" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="P57" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.01</v>
+        <v>4.51</v>
       </c>
       <c r="R57" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S57" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="T57" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U57" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V57" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W57" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X57" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="Y57" t="n">
         <v>2.2</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>4.02</v>
+        <v>3.76</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="M58" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="N58" t="n">
-        <v>3.56</v>
+        <v>4.33</v>
       </c>
       <c r="O58" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="P58" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.9</v>
+        <v>5.01</v>
       </c>
       <c r="R58" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W58" t="n">
         <v>1.4</v>
       </c>
-      <c r="S58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X58" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="Y58" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC58" t="n">
         <v>1.94</v>
       </c>
-      <c r="Z58" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD58" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N59" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="O59" t="n">
-        <v>2.64</v>
+        <v>3.32</v>
       </c>
       <c r="P59" t="n">
         <v>1.9</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.02</v>
+        <v>3.45</v>
       </c>
       <c r="R59" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="S59" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="T59" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="U59" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V59" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W59" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="X59" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.71</v>
+        <v>1.4</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="M60" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="O60" t="n">
-        <v>3.32</v>
+        <v>2.64</v>
       </c>
       <c r="P60" t="n">
         <v>1.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.45</v>
+        <v>5.02</v>
       </c>
       <c r="R60" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="S60" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="T60" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="U60" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V60" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W60" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="X60" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA60" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="M63" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N63" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="O63" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="P63" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>3.61</v>
       </c>
       <c r="R63" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S63" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="T63" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="U63" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W63" t="n">
         <v>1.32</v>
       </c>
-      <c r="V63" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X63" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AA63" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N64" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O64" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="P64" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="R64" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S64" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="T64" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="U64" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V64" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W64" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="X64" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AA64" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="N65" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O65" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q65" t="n">
         <v>3.07</v>
       </c>
-      <c r="P65" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3.61</v>
-      </c>
       <c r="R65" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S65" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="T65" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="U65" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V65" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W65" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="X65" t="n">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -9013,12 +9013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.26</v>
+        <v>1.69</v>
       </c>
       <c r="M67" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>3.07</v>
+        <v>4.3</v>
       </c>
       <c r="O67" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P67" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="R67" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="S67" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="T67" t="n">
-        <v>3.35</v>
+        <v>2.56</v>
       </c>
       <c r="U67" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="V67" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W67" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="X67" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.53</v>
+        <v>2.06</v>
       </c>
       <c r="AA67" t="n">
-        <v>4.64</v>
+        <v>2.9</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="AK67" s="3" t="n">
-        <v>45964.75</v>
+        <v>45964.79166666666</v>
       </c>
     </row>
     <row r="68">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N68" t="n">
-        <v>3.86</v>
+        <v>3.07</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -678,31 +678,31 @@
         <v>2.23</v>
       </c>
       <c r="O2" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="T2" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
         <v>3.4</v>
@@ -711,19 +711,19 @@
         <v>1.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,34 +2346,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="N15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
         <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
         <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
         <v>2.59</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
         <v>1.06</v>
@@ -2385,22 +2385,22 @@
         <v>3</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AH15" t="n">
         <v>1.33</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.59</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.85</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.08</v>
+        <v>5.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.63</v>
+        <v>2.27</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.98</v>
+        <v>4.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>1.17</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>4.7</v>
+        <v>4.59</v>
       </c>
       <c r="O22" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="P22" t="n">
         <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.21</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
         <v>1.27</v>
@@ -3273,31 +3273,31 @@
         <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
         <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AA22" t="n">
         <v>2.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC22" t="n">
         <v>1.67</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH22" t="n">
         <v>2.25</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="O26" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -3792,22 +3792,22 @@
         <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
         <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA26" t="n">
         <v>3.95</v>
@@ -3816,7 +3816,7 @@
         <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
         <v>1.75</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,78 +4152,78 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="M29" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
         <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
         <v>3.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB29" t="n">
         <v>1.4</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AI29" t="n">
         <v>0</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45964.57291666666</v>
+        <v>45964.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,62 +4281,62 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.94</v>
+        <v>2.01</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD30" t="n">
         <v>2.15</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
-        <v>2.38</v>
+        <v>3.16</v>
       </c>
       <c r="P31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD31" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.3</v>
       </c>
-      <c r="X31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH31" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="O32" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="T32" t="n">
-        <v>2.72</v>
+        <v>2.93</v>
       </c>
       <c r="U32" t="n">
         <v>1.38</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA32" t="n">
         <v>3.4</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.2</v>
       </c>
       <c r="AB32" t="n">
         <v>1.29</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,19 +4668,19 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O33" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
         <v>3.6</v>
@@ -4689,40 +4689,40 @@
         <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T33" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="U33" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X33" t="n">
         <v>3.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="Z33" t="n">
         <v>1.83</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.73</v>
+        <v>2.51</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="N34" t="n">
-        <v>4.58</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.85</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S34" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="T34" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
         <v>1.05</v>
       </c>
       <c r="W34" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="X34" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="Y34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z34" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z34" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AC34" t="n">
         <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="M35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X35" t="n">
         <v>3.4</v>
       </c>
-      <c r="N35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.9</v>
-      </c>
       <c r="Y35" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="M36" t="n">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="N36" t="n">
-        <v>3.17</v>
+        <v>4.58</v>
       </c>
       <c r="O36" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P36" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.86</v>
+        <v>4.85</v>
       </c>
       <c r="R36" t="n">
         <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T36" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="U36" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W36" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X36" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.39</v>
+        <v>3.94</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.65</v>
+        <v>1.62</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="P37" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>2.73</v>
+        <v>3.98</v>
       </c>
       <c r="T37" t="n">
-        <v>2.96</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="V37" t="n">
         <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>1.31</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.76</v>
+        <v>2.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.28</v>
+        <v>1.92</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="M38" t="n">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="N38" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="O38" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>2.51</v>
+        <v>3.54</v>
       </c>
       <c r="U38" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W38" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="X38" t="n">
-        <v>3.9</v>
+        <v>2.59</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.75</v>
+        <v>4.55</v>
       </c>
       <c r="AB38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH38" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45964.58333333334</v>
+        <v>45964.60416666666</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="P39" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="T39" t="n">
-        <v>3.54</v>
+        <v>2.56</v>
       </c>
       <c r="U39" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="V39" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="X39" t="n">
-        <v>2.59</v>
+        <v>3.74</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.55</v>
+        <v>2.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45964.60416666666</v>
+        <v>45964.61458333334</v>
       </c>
     </row>
     <row r="40">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S40" t="n">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="T40" t="n">
-        <v>2.67</v>
+        <v>2.18</v>
       </c>
       <c r="U40" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W40" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.83</v>
+        <v>2.38</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="M41" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2.66</v>
+        <v>3.25</v>
       </c>
       <c r="O41" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="P41" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.95</v>
+        <v>3.84</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="T41" t="n">
-        <v>2.29</v>
+        <v>2.44</v>
       </c>
       <c r="U41" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
         <v>1.2</v>
       </c>
       <c r="X41" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC41" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD41" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>1.3</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
         <v>2.85</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="R42" t="n">
+      <c r="U42" t="n">
         <v>1.45</v>
       </c>
-      <c r="S42" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T42" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.3</v>
-      </c>
       <c r="V42" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="X42" t="n">
-        <v>2.83</v>
+        <v>3.65</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S43" t="n">
         <v>3.15</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="O43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.81</v>
-      </c>
       <c r="T43" t="n">
-        <v>3.07</v>
+        <v>2.53</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="X43" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="Y43" t="n">
         <v>1.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,62 +6087,62 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M44" t="n">
+        <v>4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD44" t="n">
         <v>2.2</v>
       </c>
-      <c r="M44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.56</v>
+        <v>1.17</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.14</v>
+        <v>3.56</v>
       </c>
       <c r="R46" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S46" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>2.31</v>
+        <v>2.66</v>
       </c>
       <c r="U46" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="X46" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="O48" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P48" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="S48" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="T48" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="U48" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W48" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="X48" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6732,16 +6732,16 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="M49" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="O49" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P49" t="n">
         <v>2</v>
@@ -6750,16 +6750,16 @@
         <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
         <v>2.44</v>
       </c>
       <c r="T49" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="U49" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V49" t="n">
         <v>1.03</v>
@@ -6768,25 +6768,25 @@
         <v>1.45</v>
       </c>
       <c r="X49" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="Y49" t="n">
         <v>2.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AA49" t="n">
         <v>4.3</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC49" t="n">
         <v>1.95</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.5</v>
+        <v>1.55</v>
       </c>
       <c r="M52" t="n">
         <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="O52" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P52" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X52" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA52" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q52" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X52" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB52" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.89</v>
+        <v>2.25</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.49</v>
+        <v>2.15</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,77 +7377,77 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.55</v>
+        <v>2.31</v>
       </c>
       <c r="M54" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="N54" t="n">
-        <v>4.1</v>
+        <v>2.64</v>
       </c>
       <c r="O54" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="P54" t="n">
         <v>2.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.84</v>
+        <v>3.1</v>
       </c>
       <c r="R54" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S54" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="T54" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="U54" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="V54" t="n">
         <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X54" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Y54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB54" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z54" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>2.15</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="M55" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N55" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="O55" t="n">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="P55" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.01</v>
+        <v>5.02</v>
       </c>
       <c r="R55" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="S55" t="n">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="T55" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="U55" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V55" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W55" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="X55" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="M56" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="O56" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="P56" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.9</v>
+        <v>4.44</v>
       </c>
       <c r="R56" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S56" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="T56" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U56" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V56" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W56" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="X56" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AA56" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="AB56" t="n">
         <v>1.25</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="M57" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>3.35</v>
+        <v>3.92</v>
       </c>
       <c r="O57" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T57" t="n">
         <v>2.63</v>
       </c>
-      <c r="P57" t="n">
+      <c r="U57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X57" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y57" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q57" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z57" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.76</v>
+        <v>3.46</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7893,37 +7893,37 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="M58" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N58" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="O58" t="n">
         <v>2.48</v>
       </c>
       <c r="P58" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.01</v>
+        <v>4.6</v>
       </c>
       <c r="R58" t="n">
         <v>1.45</v>
       </c>
       <c r="S58" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="T58" t="n">
         <v>3.1</v>
       </c>
       <c r="U58" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V58" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W58" t="n">
         <v>1.4</v>
@@ -7932,10 +7932,10 @@
         <v>2.88</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA58" t="n">
         <v>4.02</v>
@@ -7944,7 +7944,7 @@
         <v>1.2</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD58" t="n">
         <v>1.75</v>
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH58" t="n">
         <v>1.83</v>
@@ -8022,25 +8022,25 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="M59" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="N59" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="O59" t="n">
         <v>3.32</v>
       </c>
       <c r="P59" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S59" t="n">
         <v>2.38</v>
@@ -8055,28 +8055,28 @@
         <v>1.04</v>
       </c>
       <c r="W59" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="X59" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AB59" t="n">
         <v>1.16</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="M60" t="n">
         <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>4.05</v>
+        <v>2.9</v>
       </c>
       <c r="O60" t="n">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="P60" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.02</v>
+        <v>3.62</v>
       </c>
       <c r="R60" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="S60" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="T60" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="U60" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V60" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W60" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="X60" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AA60" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="M63" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q63" t="n">
         <v>3.25</v>
       </c>
-      <c r="N63" t="n">
+      <c r="R63" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X63" t="n">
         <v>2.75</v>
       </c>
-      <c r="O63" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="P63" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T63" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X63" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Y63" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA63" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,77 +8667,77 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="M64" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="N64" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O64" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T64" t="n">
         <v>3.4</v>
       </c>
-      <c r="P64" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T64" t="n">
-        <v>3.36</v>
-      </c>
       <c r="U64" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V64" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W64" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X64" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
         <v>1.4</v>
       </c>
-      <c r="X64" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
+      <c r="AH64" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,77 +8796,77 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X65" t="n">
         <v>2.99</v>
       </c>
-      <c r="M65" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O65" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="R65" t="n">
+      <c r="Y65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH65" t="n">
         <v>1.5</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -9054,22 +9054,22 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="M67" t="n">
         <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>4.3</v>
+        <v>4.23</v>
       </c>
       <c r="O67" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="P67" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="R67" t="n">
         <v>1.32</v>
@@ -9078,53 +9078,53 @@
         <v>3.05</v>
       </c>
       <c r="T67" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U67" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V67" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W67" t="n">
         <v>1.25</v>
       </c>
       <c r="X67" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="Y67" t="n">
         <v>1.75</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC67" t="n">
         <v>1.71</v>
       </c>
       <c r="AD67" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH67" t="n">
         <v>2</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="M2" t="n">
         <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
         <v>3.25</v>
@@ -687,13 +687,13 @@
         <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="U2" t="n">
         <v>1.38</v>
@@ -711,7 +711,7 @@
         <v>1.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AA2" t="n">
         <v>3.14</v>
@@ -723,7 +723,7 @@
         <v>1.77</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
         <v>1.4</v>
@@ -936,10 +936,10 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="P4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
         <v>3.88</v>
@@ -966,13 +966,13 @@
         <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="Z4" t="n">
         <v>1.56</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.08</v>
+        <v>3.98</v>
       </c>
       <c r="AB4" t="n">
         <v>1.17</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.16</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>1.59</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>1.65</v>
+        <v>4.85</v>
       </c>
       <c r="O16" t="n">
-        <v>5.45</v>
+        <v>2.08</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.27</v>
+        <v>4.63</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.03</v>
+        <v>2.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.17</v>
+        <v>2.07</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,77 +2604,77 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.59</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA17" t="n">
         <v>3.7</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.98</v>
-      </c>
       <c r="AB17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.07</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3006,13 +3006,13 @@
         <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="T20" t="n">
         <v>3.68</v>
@@ -3021,7 +3021,7 @@
         <v>1.21</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
         <v>1.6</v>
@@ -3033,13 +3033,13 @@
         <v>2.49</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
         <v>5.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AC20" t="n">
         <v>2.2</v>
@@ -3138,7 +3138,7 @@
         <v>3.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
         <v>2.31</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>4.59</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
         <v>2</v>
@@ -3288,10 +3288,10 @@
         <v>4.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
         <v>2.6</v>
@@ -3510,58 +3510,58 @@
         <v>1.61</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="O24" t="n">
         <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>4.39</v>
       </c>
       <c r="R24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>7.39</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3645,52 +3645,52 @@
         <v>3.73</v>
       </c>
       <c r="O25" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.42</v>
+        <v>4.58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>2.82</v>
+        <v>3.06</v>
       </c>
       <c r="T25" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="X25" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N26" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O26" t="n">
         <v>5.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -3792,34 +3792,34 @@
         <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
         <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>2.83</v>
+        <v>3.01</v>
       </c>
       <c r="Y26" t="n">
         <v>2.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA26" t="n">
         <v>3.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC26" t="n">
         <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3903,31 +3903,31 @@
         <v>2.13</v>
       </c>
       <c r="O27" t="n">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
         <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="R27" t="n">
         <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="T27" t="n">
         <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
         <v>3.8</v>
@@ -3939,16 +3939,16 @@
         <v>2</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC27" t="n">
         <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="M29" t="n">
         <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.79</v>
+        <v>3.16</v>
       </c>
       <c r="P29" t="n">
         <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.58</v>
+        <v>2.99</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
         <v>3.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="Z29" t="n">
         <v>2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="O30" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S30" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X31" t="n">
         <v>3.4</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.9</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N32" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.3</v>
       </c>
-      <c r="X32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH32" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.12</v>
+        <v>3.65</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.05</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
-        <v>2.76</v>
+        <v>3.8</v>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="R33" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC33" t="n">
         <v>1.38</v>
       </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AD33" t="n">
-        <v>2.05</v>
+        <v>2.97</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,58 +4797,58 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.51</v>
+        <v>1.83</v>
       </c>
       <c r="M34" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V34" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W34" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Z34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
         <v>1.91</v>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.49</v>
+        <v>2.02</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>3.25</v>
+        <v>4.58</v>
       </c>
       <c r="O35" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>4.85</v>
       </c>
       <c r="R35" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="T35" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U35" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="V35" t="n">
         <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="X35" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="M36" t="n">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="N36" t="n">
-        <v>4.58</v>
+        <v>3.17</v>
       </c>
       <c r="O36" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.85</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
         <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="T36" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X36" t="n">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.94</v>
+        <v>2.12</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="S37" t="n">
-        <v>3.98</v>
+        <v>2.93</v>
       </c>
       <c r="T37" t="n">
-        <v>2.06</v>
+        <v>2.72</v>
       </c>
       <c r="U37" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>6.5</v>
+        <v>3.28</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.9</v>
+        <v>1.83</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.92</v>
+        <v>3.08</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5313,16 +5313,16 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P38" t="n">
         <v>1.9</v>
@@ -5337,31 +5337,31 @@
         <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="U38" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V38" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W38" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X38" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="Y38" t="n">
         <v>2.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
         <v>4.55</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AC38" t="n">
         <v>1.95</v>
@@ -5383,7 +5383,7 @@
         <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5451,10 +5451,10 @@
         <v>3.1</v>
       </c>
       <c r="O39" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="P39" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="Q39" t="n">
         <v>3.5</v>
@@ -5463,13 +5463,13 @@
         <v>1.33</v>
       </c>
       <c r="S39" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="T39" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U39" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V39" t="n">
         <v>1.05</v>
@@ -5478,22 +5478,22 @@
         <v>1.22</v>
       </c>
       <c r="X39" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="Y39" t="n">
         <v>1.76</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AA39" t="n">
         <v>2.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AD39" t="n">
         <v>2.2</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="O40" t="n">
         <v>2.95</v>
@@ -5613,19 +5613,19 @@
         <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AA40" t="n">
         <v>2.38</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC40" t="n">
         <v>1.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
         <v>1.31</v>
@@ -5727,7 +5727,7 @@
         <v>2.44</v>
       </c>
       <c r="U41" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V41" t="n">
         <v>1.04</v>
@@ -5742,19 +5742,19 @@
         <v>1.71</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="O42" t="n">
-        <v>3.69</v>
+        <v>4.95</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="T42" t="n">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="U42" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="X42" t="n">
-        <v>3.65</v>
+        <v>4.97</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O43" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="R43" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="T43" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="V43" t="n">
         <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X43" t="n">
-        <v>4.05</v>
+        <v>3.42</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="O44" t="n">
-        <v>4.95</v>
+        <v>2.86</v>
       </c>
       <c r="P44" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.05</v>
+        <v>3.54</v>
       </c>
       <c r="R44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.25</v>
       </c>
-      <c r="S44" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X44" t="n">
-        <v>4.97</v>
+        <v>3.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.3</v>
+        <v>2.97</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.58</v>
+        <v>2.87</v>
       </c>
       <c r="N45" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="O45" t="n">
-        <v>2.19</v>
+        <v>3.4</v>
       </c>
       <c r="P45" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="T45" t="n">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="U45" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="V45" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W45" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="X45" t="n">
-        <v>4.96</v>
+        <v>2.99</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.35</v>
+        <v>3.55</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,62 +6345,62 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X46" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD46" t="n">
         <v>2.2</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X46" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,77 +6474,77 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.85</v>
+        <v>1.86</v>
       </c>
       <c r="M47" t="n">
-        <v>3.21</v>
+        <v>3.58</v>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="O47" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="P47" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="R47" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S47" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="T47" t="n">
-        <v>2.82</v>
+        <v>2.31</v>
       </c>
       <c r="U47" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W47" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="X47" t="n">
-        <v>3.08</v>
+        <v>5.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.28</v>
+        <v>2.35</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH47" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S48" t="n">
+        <v>3</v>
+      </c>
+      <c r="T48" t="n">
         <v>2.85</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U48" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="V48" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W48" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="X48" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="O49" t="n">
         <v>3.34</v>
@@ -6774,7 +6774,7 @@
         <v>2.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AA49" t="n">
         <v>4.3</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="O52" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="P52" t="n">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.84</v>
+        <v>6.31</v>
       </c>
       <c r="R52" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="S52" t="n">
-        <v>3.44</v>
+        <v>2.39</v>
       </c>
       <c r="T52" t="n">
-        <v>2.31</v>
+        <v>3.3</v>
       </c>
       <c r="U52" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="V52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W52" t="n">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="X52" t="n">
-        <v>4.75</v>
+        <v>2.52</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.35</v>
+        <v>4.3</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="M53" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N53" t="n">
-        <v>6.1</v>
+        <v>2.33</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.31</v>
+        <v>1.55</v>
       </c>
       <c r="M54" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="O54" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="P54" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.1</v>
+        <v>4.84</v>
       </c>
       <c r="R54" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S54" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T54" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="U54" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="V54" t="n">
         <v>1.03</v>
       </c>
       <c r="W54" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X54" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="M55" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="N55" t="n">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="P55" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.02</v>
+        <v>4.66</v>
       </c>
       <c r="R55" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="T55" t="n">
-        <v>3.44</v>
+        <v>2.63</v>
       </c>
       <c r="U55" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V55" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="X55" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.48</v>
+        <v>1.94</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AA55" t="n">
-        <v>4.1</v>
+        <v>3.46</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N56" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O56" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC56" t="n">
         <v>2.07</v>
       </c>
-      <c r="M56" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O56" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="P56" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T56" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AD56" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,77 +7764,77 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="N57" t="n">
-        <v>3.92</v>
+        <v>2.67</v>
       </c>
       <c r="O57" t="n">
-        <v>2.51</v>
+        <v>3.32</v>
       </c>
       <c r="P57" t="n">
         <v>2.05</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.66</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S57" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="T57" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="U57" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH57" t="n">
         <v>1.4</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X57" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="M58" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="N58" t="n">
-        <v>4.27</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
-        <v>2.48</v>
+        <v>2.98</v>
       </c>
       <c r="P58" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.6</v>
+        <v>3.82</v>
       </c>
       <c r="R58" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S58" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="T58" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="U58" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V58" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W58" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X58" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AA58" t="n">
-        <v>4.02</v>
+        <v>3.5</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC58" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,77 +8022,77 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M59" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.67</v>
+        <v>3.78</v>
       </c>
       <c r="O59" t="n">
-        <v>3.32</v>
+        <v>2.66</v>
       </c>
       <c r="P59" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>4.44</v>
       </c>
       <c r="R59" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S59" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="T59" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U59" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V59" t="n">
         <v>1.04</v>
       </c>
       <c r="W59" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="X59" t="n">
         <v>2.74</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AC59" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AD59" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH59" t="n">
         <v>1.66</v>
-      </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG59" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>1.37</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N60" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="O60" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="P60" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y60" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q60" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S60" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T60" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X60" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>2.06</v>
-      </c>
       <c r="Z60" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.5</v>
+        <v>4.06</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.81</v>
+        <v>1.58</v>
       </c>
       <c r="M61" t="n">
-        <v>3.11</v>
+        <v>4.1</v>
       </c>
       <c r="N61" t="n">
-        <v>2.26</v>
+        <v>5.7</v>
       </c>
       <c r="O61" t="n">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="P61" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.9</v>
+        <v>4.84</v>
       </c>
       <c r="R61" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S61" t="n">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
       <c r="T61" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U61" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V61" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W61" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X61" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA61" t="n">
         <v>3.3</v>
       </c>
-      <c r="Y61" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AB61" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.55</v>
+        <v>2.81</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="N62" t="n">
-        <v>5.8</v>
+        <v>2.26</v>
       </c>
       <c r="O62" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="P62" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="R62" t="n">
         <v>1.36</v>
       </c>
       <c r="S62" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T62" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U62" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V62" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W62" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X62" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH62" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,77 +8538,77 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="M63" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="N63" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O63" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T63" t="n">
         <v>3.4</v>
       </c>
-      <c r="P63" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T63" t="n">
-        <v>3.36</v>
-      </c>
       <c r="U63" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V63" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W63" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X63" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
         <v>1.4</v>
       </c>
-      <c r="X63" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG63" t="n">
+      <c r="AH63" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,77 +8667,77 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.99</v>
+        <v>2.37</v>
       </c>
       <c r="M64" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O64" t="n">
-        <v>3.82</v>
+        <v>3</v>
       </c>
       <c r="P64" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="R64" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S64" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T64" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U64" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="V64" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W64" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="X64" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="Z64" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH64" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="M65" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P65" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.61</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S65" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="T65" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="U65" t="n">
         <v>1.32</v>
       </c>
       <c r="V65" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W65" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="X65" t="n">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8937,22 +8937,22 @@
         <v>3</v>
       </c>
       <c r="P66" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="Q66" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T66" t="n">
         <v>3.75</v>
       </c>
-      <c r="R66" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S66" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T66" t="n">
-        <v>3.45</v>
-      </c>
       <c r="U66" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="V66" t="n">
         <v>1.13</v>
@@ -8973,13 +8973,13 @@
         <v>5.68</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC66" t="n">
         <v>2.15</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M67" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N67" t="n">
-        <v>4.23</v>
+        <v>4.5</v>
       </c>
       <c r="O67" t="n">
         <v>2.17</v>
@@ -9069,10 +9069,10 @@
         <v>2.33</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="R67" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S67" t="n">
         <v>3.05</v>
@@ -9081,16 +9081,16 @@
         <v>2.5</v>
       </c>
       <c r="U67" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W67" t="n">
         <v>1.25</v>
       </c>
       <c r="X67" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="Y67" t="n">
         <v>1.75</v>
@@ -9099,13 +9099,13 @@
         <v>2.05</v>
       </c>
       <c r="AA67" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD67" t="n">
         <v>2.05</v>
@@ -9192,7 +9192,7 @@
         <v>3.07</v>
       </c>
       <c r="O68" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P68" t="n">
         <v>1.95</v>
@@ -9207,13 +9207,13 @@
         <v>2.41</v>
       </c>
       <c r="T68" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U68" t="n">
         <v>1.27</v>
       </c>
       <c r="V68" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="W68" t="n">
         <v>1.44</v>
@@ -9237,7 +9237,7 @@
         <v>1.95</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>4.8</v>
       </c>
       <c r="R69" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S69" t="n">
         <v>2.59</v>
@@ -9339,16 +9339,16 @@
         <v>3.1</v>
       </c>
       <c r="U69" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V69" t="n">
         <v>1.06</v>
       </c>
       <c r="W69" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X69" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="Y69" t="n">
         <v>2.2</v>
@@ -9360,13 +9360,13 @@
         <v>3.92</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
         <v>1.44</v>
@@ -954,16 +954,16 @@
         <v>3.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
         <v>2.15</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>3.04</v>
@@ -1734,10 +1734,10 @@
         <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="Y10" t="n">
         <v>2.59</v>
@@ -1752,10 +1752,10 @@
         <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
         <v>1.6</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.5</v>
       </c>
-      <c r="N15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5.1</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.27</v>
+        <v>2.91</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.59</v>
+        <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.85</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.08</v>
+        <v>5.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.63</v>
+        <v>2.27</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.98</v>
+        <v>4.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.07</v>
+        <v>1.17</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,55 +2733,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
         <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>2.93</v>
       </c>
       <c r="T18" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="U18" t="n">
         <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
         <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
         <v>1.83</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>2.39</v>
+        <v>3.35</v>
       </c>
       <c r="T20" t="n">
-        <v>3.68</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="X20" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>2.23</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.06</v>
+        <v>2.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.7</v>
+        <v>4.02</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>2.69</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>2.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>3.68</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="X22" t="n">
-        <v>4.2</v>
+        <v>2.49</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.6</v>
+        <v>5.06</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="O27" t="n">
         <v>3.4</v>
@@ -3909,40 +3909,40 @@
         <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>3.21</v>
+        <v>2.96</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
         <v>2.66</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
         <v>1.62</v>
@@ -3964,7 +3964,7 @@
         <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="M29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X29" t="n">
         <v>3.4</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.9</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.51</v>
+        <v>1.73</v>
       </c>
       <c r="M30" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
         <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="X30" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.45</v>
+        <v>3.03</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC30" t="n">
         <v>1.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q31" t="n">
         <v>3.25</v>
       </c>
-      <c r="O31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.6</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T31" t="n">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P32" t="n">
         <v>2.15</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q32" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
         <v>1.46</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4797,16 +4797,16 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="M34" t="n">
         <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="O34" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="P34" t="n">
         <v>2.2</v>
@@ -4815,34 +4815,34 @@
         <v>4.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
         <v>2.81</v>
       </c>
       <c r="T34" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V34" t="n">
         <v>1.06</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
         <v>3.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="AB34" t="n">
         <v>1.29</v>
@@ -4867,7 +4867,7 @@
         <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>4.58</v>
+        <v>2.65</v>
       </c>
       <c r="O35" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.85</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S35" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="T35" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="U35" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="V35" t="n">
         <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AC35" t="n">
         <v>1.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,62 +5055,62 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="M36" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="O36" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="P36" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q36" t="n">
         <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S36" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="U36" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X36" t="n">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="Z36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD36" t="n">
         <v>2.05</v>
       </c>
-      <c r="AA36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="N37" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="T37" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="V37" t="n">
         <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X37" t="n">
-        <v>3.28</v>
+        <v>3.76</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.08</v>
+        <v>2.66</v>
       </c>
       <c r="AB37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC37" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="O39" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="P39" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="T39" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="U39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.44</v>
       </c>
-      <c r="V39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="M40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q40" t="n">
         <v>3.6</v>
       </c>
-      <c r="N40" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>3.16</v>
-      </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S40" t="n">
-        <v>3.24</v>
+        <v>3.06</v>
       </c>
       <c r="T40" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="U40" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="V40" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X40" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="M41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q41" t="n">
         <v>3.5</v>
       </c>
-      <c r="N41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>3.6</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>3.06</v>
+        <v>3.18</v>
       </c>
       <c r="T41" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="U41" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V41" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X41" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,62 +5829,62 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="O42" t="n">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="P42" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD42" t="n">
         <v>2.05</v>
       </c>
-      <c r="R42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X42" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O43" t="n">
-        <v>4.2</v>
+        <v>2.86</v>
       </c>
       <c r="P43" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.55</v>
+        <v>3.54</v>
       </c>
       <c r="R43" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S43" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="T43" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="U43" t="n">
         <v>1.41</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X43" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="Y43" t="n">
         <v>1.82</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,77 +6087,77 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="M44" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O44" t="n">
         <v>3.4</v>
       </c>
-      <c r="N44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.86</v>
-      </c>
       <c r="P44" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="R44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH44" t="n">
         <v>1.35</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.52</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="M45" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O45" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U45" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="V45" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W45" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="X45" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.86</v>
+        <v>4.6</v>
       </c>
       <c r="M47" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="O47" t="n">
-        <v>2.3</v>
+        <v>4.95</v>
       </c>
       <c r="P47" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="R47" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="T47" t="n">
         <v>2.31</v>
       </c>
       <c r="U47" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="V47" t="n">
         <v>1.03</v>
       </c>
       <c r="W47" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X47" t="n">
-        <v>5.02</v>
+        <v>4.97</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="O48" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="P48" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="R48" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="T48" t="n">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="U48" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="V48" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="X48" t="n">
-        <v>3.22</v>
+        <v>4.6</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.68</v>
+        <v>2.32</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6732,16 +6732,16 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="M49" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="O49" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P49" t="n">
         <v>2</v>
@@ -6750,13 +6750,13 @@
         <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S49" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="T49" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U49" t="n">
         <v>1.3</v>
@@ -6774,7 +6774,7 @@
         <v>2.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AA49" t="n">
         <v>4.3</v>
@@ -6783,10 +6783,10 @@
         <v>1.18</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,62 +7119,62 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="M52" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N52" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="O52" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X52" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD52" t="n">
         <v>2.25</v>
       </c>
-      <c r="P52" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X52" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AE52" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="M53" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="N53" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="O53" t="n">
         <v>2.75</v>
       </c>
       <c r="P53" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S53" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="T53" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="U53" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="V53" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W53" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X53" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,77 +7377,77 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="N54" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="O54" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="P54" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.84</v>
+        <v>2.88</v>
       </c>
       <c r="R54" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S54" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="T54" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="U54" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="V54" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X54" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AB54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>2.2</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,77 +7506,77 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="M55" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N55" t="n">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="O55" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="P55" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="R55" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="S55" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="T55" t="n">
-        <v>2.63</v>
+        <v>3.35</v>
       </c>
       <c r="U55" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="V55" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W55" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="X55" t="n">
-        <v>3.14</v>
+        <v>2.58</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.94</v>
+        <v>2.48</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AD55" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH55" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.98</v>
+        <v>2.85</v>
       </c>
       <c r="M56" t="n">
-        <v>3.05</v>
+        <v>2.81</v>
       </c>
       <c r="N56" t="n">
-        <v>4.05</v>
+        <v>2.67</v>
       </c>
       <c r="O56" t="n">
-        <v>2.61</v>
+        <v>3.32</v>
       </c>
       <c r="P56" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="R56" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="S56" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="T56" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="U56" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V56" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W56" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X56" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AA56" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC56" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,58 +7764,58 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="M57" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="N57" t="n">
-        <v>2.67</v>
+        <v>3.78</v>
       </c>
       <c r="O57" t="n">
-        <v>3.32</v>
+        <v>2.66</v>
       </c>
       <c r="P57" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>4.44</v>
       </c>
       <c r="R57" t="n">
         <v>1.46</v>
       </c>
       <c r="S57" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="T57" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U57" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V57" t="n">
         <v>1.04</v>
       </c>
       <c r="W57" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="X57" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AA57" t="n">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD57" t="n">
         <v>1.77</v>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="M58" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="O58" t="n">
-        <v>2.98</v>
+        <v>2.51</v>
       </c>
       <c r="P58" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.82</v>
+        <v>4.6</v>
       </c>
       <c r="R58" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S58" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T58" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="U58" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V58" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W58" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X58" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AA58" t="n">
-        <v>3.5</v>
+        <v>4.06</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="M59" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N59" t="n">
-        <v>3.78</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="P59" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.44</v>
+        <v>3.82</v>
       </c>
       <c r="R59" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S59" t="n">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="T59" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="U59" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V59" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W59" t="n">
         <v>1.35</v>
       </c>
       <c r="X59" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="M60" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N60" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="O60" t="n">
         <v>2.51</v>
       </c>
       <c r="P60" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="R60" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S60" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="T60" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="U60" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V60" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W60" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="X60" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AA60" t="n">
-        <v>4.06</v>
+        <v>3.46</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AC60" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.58</v>
+        <v>2.87</v>
       </c>
       <c r="M61" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>5.7</v>
+        <v>2.25</v>
       </c>
       <c r="O61" t="n">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="P61" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.84</v>
+        <v>2.94</v>
       </c>
       <c r="R61" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S61" t="n">
-        <v>3.06</v>
+        <v>2.73</v>
       </c>
       <c r="T61" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U61" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V61" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W61" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X61" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="Y61" t="n">
         <v>1.98</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH61" t="n">
-        <v>2.45</v>
+        <v>1.36</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.81</v>
+        <v>1.58</v>
       </c>
       <c r="M62" t="n">
-        <v>3.11</v>
+        <v>4.1</v>
       </c>
       <c r="N62" t="n">
-        <v>2.26</v>
+        <v>5.7</v>
       </c>
       <c r="O62" t="n">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="P62" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.9</v>
+        <v>4.84</v>
       </c>
       <c r="R62" t="n">
         <v>1.36</v>
       </c>
       <c r="S62" t="n">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
       <c r="T62" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="U62" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V62" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W62" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X62" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="Y62" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z62" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z62" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AA62" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="M63" t="n">
         <v>2.99</v>
       </c>
       <c r="N63" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="O63" t="n">
         <v>3.82</v>
@@ -8553,59 +8553,59 @@
         <v>1.95</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="S63" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="T63" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U63" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V63" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="W63" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X63" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Z63" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG63" t="n">
-        <v>1.4</v>
       </c>
       <c r="AH63" t="n">
         <v>1.36</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,77 +8667,77 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N64" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="O64" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R64" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S64" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X64" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH64" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S64" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T64" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X64" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3</v>
+      </c>
+      <c r="P65" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T65" t="n">
         <v>3.1</v>
-      </c>
-      <c r="M65" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N65" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T65" t="n">
-        <v>3.38</v>
       </c>
       <c r="U65" t="n">
         <v>1.32</v>
       </c>
       <c r="V65" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W65" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="X65" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="Z65" t="n">
         <v>1.65</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="M66" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="N66" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O66" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P66" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R66" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S66" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="T66" t="n">
         <v>3.75</v>
       </c>
       <c r="U66" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V66" t="n">
         <v>1.13</v>
       </c>
       <c r="W66" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X66" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AA66" t="n">
-        <v>5.68</v>
+        <v>5.45</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AC66" t="n">
         <v>2.15</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9192,7 +9192,7 @@
         <v>3.07</v>
       </c>
       <c r="O68" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P68" t="n">
         <v>1.95</v>
@@ -9201,7 +9201,7 @@
         <v>3.7</v>
       </c>
       <c r="R68" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S68" t="n">
         <v>2.41</v>
@@ -9213,7 +9213,7 @@
         <v>1.27</v>
       </c>
       <c r="V68" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W68" t="n">
         <v>1.44</v>
@@ -9225,7 +9225,7 @@
         <v>2.35</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AA68" t="n">
         <v>4.64</v>
@@ -9237,7 +9237,7 @@
         <v>1.95</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="M69" t="n">
-        <v>3.17</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="O69" t="n">
         <v>2.4</v>
@@ -9327,7 +9327,7 @@
         <v>2.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="R69" t="n">
         <v>1.4</v>
@@ -9348,25 +9348,25 @@
         <v>1.33</v>
       </c>
       <c r="X69" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA69" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH69" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="N2" t="n">
         <v>2.3</v>
@@ -681,22 +681,22 @@
         <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
       </c>
       <c r="R2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.38</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -705,25 +705,25 @@
         <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="Y2" t="n">
         <v>1.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AA2" t="n">
         <v>3.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
         <v>1.4</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2217,34 +2217,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>5.04</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.95</v>
+        <v>5.37</v>
       </c>
       <c r="R14" t="n">
         <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
         <v>1</v>
@@ -2253,25 +2253,25 @@
         <v>1.24</v>
       </c>
       <c r="X14" t="n">
-        <v>3.25</v>
+        <v>3.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,34 +2346,34 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="M15" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
@@ -2394,10 +2394,10 @@
         <v>3.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
         <v>1.86</v>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
         <v>1.33</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,62 +2991,62 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>3.98</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>3.35</v>
+        <v>2.31</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>3.58</v>
       </c>
       <c r="U20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.5</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AA20" t="n">
-        <v>2.6</v>
+        <v>4.79</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AC20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD20" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.09</v>
+        <v>1.53</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3645,52 +3645,52 @@
         <v>3.73</v>
       </c>
       <c r="O25" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.58</v>
+        <v>4.83</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
         <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.6</v>
+        <v>4.87</v>
       </c>
       <c r="M26" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="N26" t="n">
         <v>1.7</v>
       </c>
       <c r="O26" t="n">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R26" t="n">
         <v>1.43</v>
@@ -3801,13 +3801,13 @@
         <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="Y26" t="n">
         <v>2.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA26" t="n">
         <v>3.95</v>
@@ -3819,7 +3819,7 @@
         <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3894,43 +3894,43 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="N27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P27" t="n">
         <v>2.14</v>
       </c>
-      <c r="O27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Q27" t="n">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="R27" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="T27" t="n">
-        <v>2.59</v>
+        <v>2.23</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
         <v>1.75</v>
@@ -3939,16 +3939,16 @@
         <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.17</v>
+        <v>1.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="O29" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="T29" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U29" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.98</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.67</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>4.4</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD30" t="n">
         <v>2.25</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.95</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="M31" t="n">
         <v>3.4</v>
       </c>
       <c r="N31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S31" t="n">
         <v>2.9</v>
       </c>
-      <c r="O31" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.05</v>
-      </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X31" t="n">
-        <v>3.84</v>
+        <v>3.64</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC31" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="M32" t="n">
         <v>3.25</v>
@@ -4554,7 +4554,7 @@
         <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="R32" t="n">
         <v>1.33</v>
@@ -4563,19 +4563,19 @@
         <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U32" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
         <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="Y32" t="n">
         <v>1.74</v>
@@ -4590,10 +4590,10 @@
         <v>1.36</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
         <v>1.7</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,77 +4668,77 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X33" t="n">
         <v>3.65</v>
       </c>
-      <c r="M33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="Y33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.22</v>
       </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.84</v>
+        <v>2.18</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>4.15</v>
+        <v>3.05</v>
       </c>
       <c r="O34" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="P34" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S34" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X34" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.43</v>
+        <v>3.08</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="N35" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="P35" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="R35" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>2.73</v>
+        <v>3.17</v>
       </c>
       <c r="T35" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="U35" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="V35" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="X35" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2</v>
       </c>
-      <c r="Z35" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AA35" t="n">
-        <v>3.28</v>
+        <v>2.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.18</v>
+        <v>3.65</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.05</v>
+        <v>1.78</v>
       </c>
       <c r="O36" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="R36" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>2.77</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC36" t="n">
         <v>1.38</v>
       </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AD36" t="n">
-        <v>2.05</v>
+        <v>2.97</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="O37" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S37" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="X37" t="n">
-        <v>3.76</v>
+        <v>3.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.66</v>
+        <v>3.28</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5313,58 +5313,58 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N38" t="n">
         <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
         <v>1.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
         <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T38" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="U38" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V38" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W38" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X38" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AA38" t="n">
         <v>4.55</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD38" t="n">
         <v>1.75</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH38" t="n">
         <v>1.57</v>
@@ -5445,7 +5445,7 @@
         <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N39" t="n">
         <v>2.73</v>
@@ -5457,40 +5457,40 @@
         <v>2.23</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R39" t="n">
         <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="T39" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AC39" t="n">
         <v>1.5</v>
@@ -5589,31 +5589,31 @@
         <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="T40" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="U40" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V40" t="n">
         <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AA40" t="n">
         <v>2.66</v>
@@ -5622,10 +5622,10 @@
         <v>1.41</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH40" t="n">
         <v>1.75</v>
@@ -5709,16 +5709,16 @@
         <v>3.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="P41" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="Q41" t="n">
         <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S41" t="n">
         <v>3.18</v>
@@ -5733,25 +5733,25 @@
         <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X41" t="n">
         <v>3.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AD41" t="n">
         <v>2.2</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S42" t="n">
         <v>3</v>
       </c>
-      <c r="N42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.82</v>
-      </c>
       <c r="T42" t="n">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="U42" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W42" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="X42" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.92</v>
+        <v>3.68</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,62 +5958,62 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X43" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD43" t="n">
         <v>2.2</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="M44" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="O44" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X44" t="n">
         <v>3.4</v>
       </c>
-      <c r="P44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.99</v>
-      </c>
       <c r="Y44" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="n">
-        <v>3.69</v>
+        <v>2.3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="R45" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="T45" t="n">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="U45" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="V45" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W45" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="X45" t="n">
-        <v>3.22</v>
+        <v>4.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.68</v>
+        <v>2.32</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,62 +6345,62 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="M46" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="P46" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="R46" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S46" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="U46" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X46" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="Z46" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD46" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="M48" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.9</v>
+        <v>2.35</v>
       </c>
       <c r="O48" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="P48" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="R48" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="S48" t="n">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="T48" t="n">
-        <v>2.31</v>
+        <v>3.28</v>
       </c>
       <c r="U48" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W48" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="X48" t="n">
-        <v>4.6</v>
+        <v>2.83</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.32</v>
+        <v>3.55</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.95</v>
+        <v>1.32</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6735,7 +6735,7 @@
         <v>2.8</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="N49" t="n">
         <v>2.48</v>
@@ -6753,10 +6753,10 @@
         <v>1.43</v>
       </c>
       <c r="S49" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="T49" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="U49" t="n">
         <v>1.3</v>
@@ -6771,22 +6771,22 @@
         <v>2.62</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA49" t="n">
         <v>4.3</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="N50" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="O50" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="P50" t="n">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.31</v>
+        <v>2.88</v>
       </c>
       <c r="R50" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="S50" t="n">
-        <v>2.39</v>
+        <v>3.7</v>
       </c>
       <c r="T50" t="n">
-        <v>3.3</v>
+        <v>2.06</v>
       </c>
       <c r="U50" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="V50" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W50" t="n">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="X50" t="n">
-        <v>2.52</v>
+        <v>5.65</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.54</v>
+        <v>2.66</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.15</v>
+        <v>1.73</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.58</v>
+        <v>2.75</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,77 +7377,77 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="M54" t="n">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="N54" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="O54" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="P54" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.88</v>
+        <v>6.36</v>
       </c>
       <c r="R54" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="S54" t="n">
-        <v>3.7</v>
+        <v>2.36</v>
       </c>
       <c r="T54" t="n">
-        <v>2.06</v>
+        <v>3.32</v>
       </c>
       <c r="U54" t="n">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="V54" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W54" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
         <v>1.09</v>
       </c>
-      <c r="X54" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH54" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7509,58 +7509,58 @@
         <v>1.98</v>
       </c>
       <c r="M55" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N55" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="O55" t="n">
-        <v>2.61</v>
+        <v>2.51</v>
       </c>
       <c r="P55" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="R55" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="T55" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="U55" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="V55" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="X55" t="n">
-        <v>2.58</v>
+        <v>3.25</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA55" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="M56" t="n">
-        <v>2.81</v>
+        <v>3.01</v>
       </c>
       <c r="N56" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="O56" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.4</v>
+        <v>3.79</v>
       </c>
       <c r="R56" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="T56" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="U56" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V56" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W56" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="X56" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AA56" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="M57" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N57" t="n">
+        <v>4</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T57" t="n">
         <v>3.1</v>
       </c>
-      <c r="N57" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S57" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U57" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="V57" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W57" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X57" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.76</v>
+        <v>4.06</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="M58" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N58" t="n">
-        <v>4.1</v>
+        <v>3.57</v>
       </c>
       <c r="O58" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="P58" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.6</v>
+        <v>4.51</v>
       </c>
       <c r="R58" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S58" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="T58" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U58" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V58" t="n">
         <v>1.03</v>
       </c>
       <c r="W58" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X58" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA58" t="n">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC58" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="M59" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="O59" t="n">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="P59" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S59" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="T59" t="n">
-        <v>3.06</v>
+        <v>3.28</v>
       </c>
       <c r="U59" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="V59" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W59" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X59" t="n">
-        <v>3.05</v>
+        <v>2.43</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8154,58 +8154,58 @@
         <v>1.98</v>
       </c>
       <c r="M60" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="O60" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="P60" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.66</v>
+        <v>4.75</v>
       </c>
       <c r="R60" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S60" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="T60" t="n">
-        <v>2.63</v>
+        <v>3.34</v>
       </c>
       <c r="U60" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V60" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W60" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="X60" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O61" t="n">
         <v>3.5</v>
@@ -8295,7 +8295,7 @@
         <v>2</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="R61" t="n">
         <v>1.4</v>
@@ -8310,13 +8310,13 @@
         <v>1.39</v>
       </c>
       <c r="V61" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W61" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X61" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="Y61" t="n">
         <v>1.98</v>
@@ -8325,7 +8325,7 @@
         <v>1.86</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AB61" t="n">
         <v>1.35</v>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH61" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M62" t="n">
         <v>4.1</v>
       </c>
       <c r="N62" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="O62" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="P62" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.84</v>
+        <v>5.5</v>
       </c>
       <c r="R62" t="n">
         <v>1.36</v>
       </c>
       <c r="S62" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="T62" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U62" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V62" t="n">
         <v>1</v>
       </c>
       <c r="W62" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X62" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AC62" t="n">
         <v>1.95</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>1.21</v>
       </c>
       <c r="AH62" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="M63" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N63" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O63" t="n">
+        <v>3</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T63" t="n">
         <v>2.99</v>
       </c>
-      <c r="N63" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O63" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T63" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U63" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W63" t="n">
         <v>1.28</v>
       </c>
-      <c r="V63" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X63" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AA63" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AC63" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="M64" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="N64" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="O64" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="P64" t="n">
         <v>1.95</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="S64" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="T64" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="U64" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V64" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W64" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="X64" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AA64" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH64" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N65" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S65" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X65" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y65" t="n">
         <v>2.37</v>
-      </c>
-      <c r="M65" t="n">
-        <v>3</v>
-      </c>
-      <c r="N65" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O65" t="n">
-        <v>3</v>
-      </c>
-      <c r="P65" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S65" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T65" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X65" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>2.09</v>
       </c>
       <c r="Z65" t="n">
         <v>1.65</v>
       </c>
       <c r="AA65" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,77 +9054,77 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.68</v>
+        <v>2.26</v>
       </c>
       <c r="M67" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="N67" t="n">
-        <v>4.5</v>
+        <v>3.07</v>
       </c>
       <c r="O67" t="n">
-        <v>2.17</v>
+        <v>3.08</v>
       </c>
       <c r="P67" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.98</v>
+        <v>3.7</v>
       </c>
       <c r="R67" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="S67" t="n">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="T67" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="U67" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="V67" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W67" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="X67" t="n">
-        <v>3.75</v>
+        <v>2.59</v>
       </c>
       <c r="Y67" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD67" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z67" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB67" t="n">
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC67" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH67" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.26</v>
+        <v>1.72</v>
       </c>
       <c r="M68" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="N68" t="n">
-        <v>3.07</v>
+        <v>4.46</v>
       </c>
       <c r="O68" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P68" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="R68" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U68" t="n">
         <v>1.45</v>
       </c>
-      <c r="S68" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T68" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.27</v>
-      </c>
       <c r="V68" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W68" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="X68" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.64</v>
+        <v>3.02</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9318,28 +9318,28 @@
         <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O69" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P69" t="n">
         <v>2.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.3</v>
+        <v>4.33</v>
       </c>
       <c r="R69" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S69" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="T69" t="n">
         <v>3.1</v>
       </c>
       <c r="U69" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V69" t="n">
         <v>1.06</v>
@@ -9351,7 +9351,7 @@
         <v>2.9</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Z69" t="n">
         <v>1.65</v>
@@ -9360,13 +9360,13 @@
         <v>4.2</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH69" t="n">
         <v>1.85</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45964.89583333334</v>
+        <v>45964.85416666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -672,19 +672,19 @@
         <v>2.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O2" t="n">
         <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="R2" t="n">
         <v>1.37</v>
@@ -705,13 +705,13 @@
         <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="Y2" t="n">
         <v>1.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AA2" t="n">
         <v>3.14</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -927,52 +927,52 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T4" t="n">
         <v>3.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AB4" t="n">
         <v>1.17</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1188,7 +1188,7 @@
         <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
         <v>2.45</v>
@@ -1197,7 +1197,7 @@
         <v>3.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q6" t="n">
         <v>3.25</v>
@@ -1209,19 +1209,19 @@
         <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U6" t="n">
         <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W6" t="n">
         <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y6" t="n">
         <v>1.86</v>
@@ -1230,13 +1230,13 @@
         <v>1.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="AB6" t="n">
         <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AD6" t="n">
         <v>2.1</v>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>2.97</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>3.09</v>
       </c>
       <c r="N14" t="n">
-        <v>4.75</v>
+        <v>2.18</v>
       </c>
       <c r="O14" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.37</v>
+        <v>2.91</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="X14" t="n">
-        <v>3.63</v>
+        <v>2.92</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.82</v>
+        <v>4.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.27</v>
       </c>
-      <c r="O15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.28</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.17</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>4.02</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.4</v>
+        <v>5.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.33</v>
+        <v>3.28</v>
       </c>
       <c r="T22" t="n">
-        <v>3.68</v>
+        <v>2.39</v>
       </c>
       <c r="U22" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.52</v>
+        <v>1.2</v>
       </c>
       <c r="X22" t="n">
-        <v>2.49</v>
+        <v>4.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.06</v>
+        <v>2.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>2.06</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3510,31 +3510,31 @@
         <v>1.61</v>
       </c>
       <c r="M24" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="O24" t="n">
         <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.39</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="U24" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
@@ -3546,22 +3546,22 @@
         <v>7.39</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3645,37 +3645,37 @@
         <v>3.73</v>
       </c>
       <c r="O25" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.83</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
         <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z25" t="n">
         <v>2.17</v>
@@ -3684,13 +3684,13 @@
         <v>2.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3765,52 +3765,52 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.87</v>
+        <v>4.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.46</v>
+        <v>3.33</v>
       </c>
       <c r="N26" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O26" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
         <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AB26" t="n">
         <v>1.2</v>
@@ -3819,7 +3819,7 @@
         <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="M27" t="n">
-        <v>3.48</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P27" t="n">
         <v>2.15</v>
       </c>
-      <c r="O27" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q27" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="R27" t="n">
         <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
         <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
         <v>2.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="N29" t="n">
-        <v>4.15</v>
+        <v>3.17</v>
       </c>
       <c r="O29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>3.3</v>
+        <v>4.09</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.43</v>
+        <v>2.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P30" t="n">
         <v>2.2</v>
       </c>
-      <c r="M30" t="n">
+      <c r="Q30" t="n">
         <v>3.6</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.56</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="T30" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X30" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4413,58 +4413,58 @@
         <v>2.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="N31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S31" t="n">
         <v>3.2</v>
       </c>
-      <c r="O31" t="n">
+      <c r="T31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA31" t="n">
         <v>2.75</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U31" t="n">
+      <c r="AB31" t="n">
         <v>1.4</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC31" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="O32" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="T32" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.22</v>
       </c>
-      <c r="X32" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4680,22 +4680,22 @@
         <v>2.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.15</v>
+        <v>4.16</v>
       </c>
       <c r="R33" t="n">
         <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="T33" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="U33" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="V33" t="n">
         <v>1.05</v>
@@ -4704,10 +4704,10 @@
         <v>1.21</v>
       </c>
       <c r="X33" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Z33" t="n">
         <v>1.98</v>
@@ -4719,10 +4719,10 @@
         <v>1.33</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="P34" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R34" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>2.77</v>
+        <v>3.17</v>
       </c>
       <c r="T34" t="n">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="U34" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="X34" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M35" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>2.51</v>
+        <v>3.05</v>
       </c>
       <c r="O35" t="n">
-        <v>3.16</v>
+        <v>2.62</v>
       </c>
       <c r="P35" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S35" t="n">
-        <v>3.17</v>
+        <v>2.93</v>
       </c>
       <c r="T35" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="U35" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="V35" t="n">
         <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="X35" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="M36" t="n">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>1.78</v>
+        <v>2.62</v>
       </c>
       <c r="O36" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>2.81</v>
       </c>
       <c r="U36" t="n">
-        <v>1.88</v>
+        <v>1.37</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="X36" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.9</v>
+        <v>1.76</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.91</v>
+        <v>3.28</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.97</v>
+        <v>1.95</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.4</v>
+        <v>3.94</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P37" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="R37" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1.37</v>
+        <v>1.88</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="X37" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.76</v>
+        <v>2.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.28</v>
+        <v>1.92</v>
       </c>
       <c r="AB37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M38" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="O38" t="n">
         <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="R38" t="n">
         <v>1.44</v>
       </c>
       <c r="S38" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="U38" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V38" t="n">
         <v>1.07</v>
       </c>
       <c r="W38" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X38" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AA38" t="n">
         <v>4.55</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AC38" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5442,31 +5442,31 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="N39" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="O39" t="n">
         <v>2.95</v>
       </c>
       <c r="P39" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S39" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T39" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U39" t="n">
         <v>1.52</v>
@@ -5475,16 +5475,16 @@
         <v>1.03</v>
       </c>
       <c r="W39" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X39" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
         <v>2.51</v>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
         <v>1.53</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="N40" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="O40" t="n">
         <v>2.36</v>
@@ -5586,7 +5586,7 @@
         <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="R40" t="n">
         <v>1.3</v>
@@ -5604,28 +5604,28 @@
         <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X40" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5709,10 +5709,10 @@
         <v>3.1</v>
       </c>
       <c r="O41" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="P41" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
         <v>3.5</v>
@@ -5721,34 +5721,34 @@
         <v>1.32</v>
       </c>
       <c r="S41" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="T41" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U41" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V41" t="n">
         <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X41" t="n">
         <v>3.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
         <v>1.62</v>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5841,31 +5841,31 @@
         <v>3.69</v>
       </c>
       <c r="P42" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="T42" t="n">
         <v>2.85</v>
       </c>
       <c r="U42" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V42" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W42" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X42" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="Y42" t="n">
         <v>1.75</v>
@@ -5877,7 +5877,7 @@
         <v>3.68</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC42" t="n">
         <v>1.83</v>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5976,22 +5976,22 @@
         <v>2.8</v>
       </c>
       <c r="R43" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S43" t="n">
         <v>3.15</v>
       </c>
       <c r="T43" t="n">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="U43" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W43" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X43" t="n">
         <v>4.05</v>
@@ -6009,10 +6009,10 @@
         <v>1.38</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N44" t="n">
         <v>3.3</v>
       </c>
-      <c r="M44" t="n">
-        <v>3</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1.92</v>
-      </c>
       <c r="O44" t="n">
-        <v>4.26</v>
+        <v>2.3</v>
       </c>
       <c r="P44" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.59</v>
+        <v>3.9</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S44" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="T44" t="n">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="U44" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="V44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W44" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="X44" t="n">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.23</v>
+        <v>1.95</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="O45" t="n">
-        <v>2.3</v>
+        <v>2.86</v>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="R45" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="S45" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="T45" t="n">
-        <v>2.31</v>
+        <v>2.66</v>
       </c>
       <c r="U45" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="V45" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X45" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.32</v>
+        <v>2.97</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,37 +6345,37 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="P46" t="n">
         <v>2.2</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P46" t="n">
-        <v>2.13</v>
-      </c>
       <c r="Q46" t="n">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S46" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="T46" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="U46" t="n">
         <v>1.41</v>
       </c>
       <c r="V46" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
         <v>1.25</v>
@@ -6387,16 +6387,16 @@
         <v>1.82</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AB46" t="n">
         <v>1.33</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD46" t="n">
         <v>2.1</v>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6483,10 +6483,10 @@
         <v>1.53</v>
       </c>
       <c r="O47" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="P47" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q47" t="n">
         <v>2.05</v>
@@ -6495,13 +6495,13 @@
         <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T47" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="U47" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V47" t="n">
         <v>1.03</v>
@@ -6510,7 +6510,7 @@
         <v>1.13</v>
       </c>
       <c r="X47" t="n">
-        <v>4.97</v>
+        <v>5.3</v>
       </c>
       <c r="Y47" t="n">
         <v>1.6</v>
@@ -6528,7 +6528,7 @@
         <v>1.62</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6618,28 +6618,28 @@
         <v>2.12</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
         <v>1.46</v>
       </c>
       <c r="S48" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T48" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="U48" t="n">
         <v>1.3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="X48" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="Y48" t="n">
         <v>2.07</v>
@@ -6651,13 +6651,13 @@
         <v>3.55</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="M49" t="n">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="O49" t="n">
         <v>3.5</v>
@@ -6750,13 +6750,13 @@
         <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S49" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="T49" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="U49" t="n">
         <v>1.3</v>
@@ -6771,22 +6771,22 @@
         <v>2.62</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="AB49" t="n">
         <v>1.14</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>1.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="M50" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="N50" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="O50" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="P50" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y50" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q50" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X50" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z50" t="n">
-        <v>2.66</v>
+        <v>1.53</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.05</v>
+        <v>4.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.73</v>
+        <v>1.15</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="M51" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N51" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O51" t="n">
         <v>2.75</v>
       </c>
       <c r="P51" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R51" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S51" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="T51" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="U51" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="V51" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W51" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X51" t="n">
-        <v>4.75</v>
+        <v>5.65</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>1.25</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7122,10 +7122,10 @@
         <v>1.55</v>
       </c>
       <c r="M52" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O52" t="n">
         <v>2.15</v>
@@ -7134,7 +7134,7 @@
         <v>2.38</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.84</v>
+        <v>4.2</v>
       </c>
       <c r="R52" t="n">
         <v>1.24</v>
@@ -7149,10 +7149,10 @@
         <v>1.56</v>
       </c>
       <c r="V52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W52" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X52" t="n">
         <v>4.65</v>
@@ -7161,19 +7161,19 @@
         <v>1.57</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AA52" t="n">
         <v>2.35</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC52" t="n">
         <v>1.57</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>1.22</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,77 +7377,77 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X54" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB54" t="n">
         <v>1.57</v>
       </c>
-      <c r="M54" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N54" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T54" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W54" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AC54" t="n">
-        <v>2.23</v>
+        <v>1.44</v>
       </c>
       <c r="AD54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>2.07</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N55" t="n">
-        <v>3.9</v>
+        <v>4.08</v>
       </c>
       <c r="O55" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="P55" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X55" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y55" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q55" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X55" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>2</v>
-      </c>
       <c r="Z55" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AA55" t="n">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M56" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="P56" t="n">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.79</v>
+        <v>4.38</v>
       </c>
       <c r="R56" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S56" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="T56" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="U56" t="n">
         <v>1.31</v>
       </c>
       <c r="V56" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W56" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X56" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA56" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>1.28</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="M57" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="O57" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="P57" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="R57" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S57" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T57" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U57" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V57" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W57" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="X57" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AA57" t="n">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="M58" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N58" t="n">
-        <v>3.57</v>
+        <v>4.05</v>
       </c>
       <c r="O58" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="P58" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.51</v>
+        <v>4.75</v>
       </c>
       <c r="R58" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S58" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="T58" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="U58" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V58" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W58" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="X58" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AA58" t="n">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -8022,28 +8022,28 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="M59" t="n">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="N59" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="O59" t="n">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
       <c r="P59" t="n">
         <v>2.05</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R59" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S59" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="T59" t="n">
         <v>3.28</v>
@@ -8055,28 +8055,28 @@
         <v>1.04</v>
       </c>
       <c r="W59" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X59" t="n">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AA59" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AC59" t="n">
         <v>1.92</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="N60" t="n">
-        <v>4.05</v>
+        <v>3.56</v>
       </c>
       <c r="O60" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="P60" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="R60" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="S60" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="T60" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="U60" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V60" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W60" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="X60" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.48</v>
+        <v>1.94</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AA60" t="n">
-        <v>4.33</v>
+        <v>3.46</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AC60" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,61 +8280,61 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.87</v>
+        <v>1.55</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>2.33</v>
+        <v>5.8</v>
       </c>
       <c r="O61" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.96</v>
+        <v>5.5</v>
       </c>
       <c r="R61" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U61" t="n">
         <v>1.4</v>
       </c>
-      <c r="S61" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T61" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U61" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V61" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W61" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X61" t="n">
         <v>3.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AD61" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.59</v>
+        <v>1.21</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.33</v>
+        <v>2.28</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,77 +8409,77 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.6</v>
+        <v>2.81</v>
       </c>
       <c r="M62" t="n">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="N62" t="n">
-        <v>5.75</v>
+        <v>2.26</v>
       </c>
       <c r="O62" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="P62" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.5</v>
+        <v>2.96</v>
       </c>
       <c r="R62" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X62" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH62" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S62" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T62" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V62" t="n">
-        <v>1</v>
-      </c>
-      <c r="W62" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X62" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD62" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG62" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH62" t="n">
-        <v>2.38</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="M63" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N63" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O63" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P63" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R63" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="S63" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="T63" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U63" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V63" t="n">
         <v>1.03</v>
       </c>
       <c r="W63" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="X63" t="n">
-        <v>3.15</v>
+        <v>2.74</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AA63" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8667,25 +8667,25 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="M64" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="O64" t="n">
         <v>3.82</v>
       </c>
       <c r="P64" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R64" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="S64" t="n">
         <v>2.41</v>
@@ -8694,19 +8694,19 @@
         <v>3.5</v>
       </c>
       <c r="U64" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V64" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W64" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X64" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="Z64" t="n">
         <v>1.56</v>
@@ -8715,13 +8715,13 @@
         <v>4.6</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC64" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,61 +8796,61 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="M65" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N65" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="O65" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P65" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R65" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S65" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T65" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U65" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V65" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W65" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="X65" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AA65" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC65" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
@@ -8863,10 +8863,10 @@
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="M66" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="N66" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O66" t="n">
         <v>3.1</v>
@@ -8946,40 +8946,40 @@
         <v>1.6</v>
       </c>
       <c r="S66" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="T66" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U66" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V66" t="n">
         <v>1.13</v>
       </c>
       <c r="W66" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="X66" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AA66" t="n">
         <v>5.45</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,61 +9054,61 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.26</v>
+        <v>1.72</v>
       </c>
       <c r="M67" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="N67" t="n">
-        <v>3.07</v>
+        <v>4.5</v>
       </c>
       <c r="O67" t="n">
-        <v>3.08</v>
+        <v>2.27</v>
       </c>
       <c r="P67" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="R67" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="S67" t="n">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="T67" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="U67" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="V67" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="W67" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="X67" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AA67" t="n">
-        <v>4.64</v>
+        <v>3.02</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AC67" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AE67" t="inlineStr">
         <is>
@@ -9121,10 +9121,10 @@
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,62 +9183,62 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.72</v>
+        <v>2.26</v>
       </c>
       <c r="M68" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q68" t="n">
         <v>3.5</v>
       </c>
-      <c r="N68" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="O68" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P68" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>4.1</v>
-      </c>
       <c r="R68" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="S68" t="n">
-        <v>3.2</v>
+        <v>2.41</v>
       </c>
       <c r="T68" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="U68" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="V68" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W68" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="X68" t="n">
-        <v>3.75</v>
+        <v>2.59</v>
       </c>
       <c r="Y68" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD68" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z68" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AE68" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="N69" t="n">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="O69" t="n">
         <v>2.5</v>
@@ -9327,46 +9327,46 @@
         <v>2.1</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R69" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S69" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="T69" t="n">
         <v>3.1</v>
       </c>
       <c r="U69" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V69" t="n">
         <v>1.06</v>
       </c>
       <c r="W69" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X69" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA69" t="n">
         <v>4.2</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC69" t="n">
         <v>1.98</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>4.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>4.75</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.15</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.16</v>
-      </c>
       <c r="Q16" t="n">
-        <v>4.95</v>
+        <v>2.27</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.84</v>
+        <v>2.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.15</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>5.12</v>
       </c>
       <c r="R20" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>2.36</v>
+        <v>3.28</v>
       </c>
       <c r="T20" t="n">
-        <v>3.68</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="X20" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.42</v>
+        <v>1.77</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.15</v>
+        <v>2.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.28</v>
+        <v>1.66</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z22" t="n">
         <v>1.5</v>
       </c>
-      <c r="M22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.09</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.61</v>
       </c>
-      <c r="M24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="Z24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH24" t="n">
         <v>2</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.15</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA25" t="n">
         <v>1.83</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="M29" t="n">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>3.17</v>
+        <v>4.3</v>
       </c>
       <c r="O29" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="P29" t="n">
         <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>4.16</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="T29" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="U29" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>4.09</v>
+        <v>3.62</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,16 +4281,16 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="M30" t="n">
         <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P30" t="n">
         <v>2.2</v>
@@ -4299,43 +4299,43 @@
         <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U30" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
         <v>3.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.23</v>
+        <v>3.34</v>
       </c>
       <c r="N31" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="O31" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="X31" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z31" t="n">
         <v>1.76</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AA31" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4539,46 +4539,46 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="M32" t="n">
         <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="O32" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q32" t="n">
         <v>4.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="U32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Z32" t="n">
         <v>1.85</v>
@@ -4587,13 +4587,13 @@
         <v>3.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AC32" t="n">
         <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,62 +4668,62 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="N33" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD33" t="n">
         <v>2.25</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.45</v>
+        <v>3.94</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="O34" t="n">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="P34" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X34" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.85</v>
       </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.31</v>
+        <v>2.97</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.41</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,16 +4926,16 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
         <v>2.2</v>
@@ -4944,43 +4944,43 @@
         <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S35" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="T35" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U35" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X35" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="AB35" t="n">
         <v>1.28</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="N36" t="n">
-        <v>2.62</v>
+        <v>3.17</v>
       </c>
       <c r="O36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
         <v>3</v>
       </c>
-      <c r="P36" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.77</v>
-      </c>
       <c r="T36" t="n">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="U36" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="X36" t="n">
-        <v>3.3</v>
+        <v>4.09</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.94</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
-        <v>3.6</v>
+        <v>3.16</v>
       </c>
       <c r="P37" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.16</v>
+        <v>2.85</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="U37" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="X37" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.37</v>
+        <v>1.71</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.85</v>
+        <v>1.97</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.97</v>
+        <v>2.31</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5313,22 +5313,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="N38" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="O38" t="n">
         <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="R38" t="n">
         <v>1.44</v>
@@ -5337,37 +5337,37 @@
         <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="U38" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V38" t="n">
         <v>1.07</v>
       </c>
       <c r="W38" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X38" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="M39" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA39" t="n">
         <v>2.66</v>
       </c>
-      <c r="O39" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.51</v>
-      </c>
       <c r="AB39" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,58 +5571,58 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="M40" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
         <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="T40" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="U40" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X40" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD40" t="n">
         <v>2.2</v>
@@ -5641,7 +5641,7 @@
         <v>1.23</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,62 +5700,62 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N41" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q41" t="n">
         <v>3.1</v>
       </c>
-      <c r="O41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S41" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD41" t="n">
         <v>2.45</v>
       </c>
-      <c r="U41" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y42" t="n">
         <v>2.07</v>
       </c>
-      <c r="O42" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R42" t="n">
+      <c r="Z42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH42" t="n">
         <v>1.38</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.28</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.62</v>
+        <v>4.6</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="O43" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="P43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T43" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q43" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.33</v>
-      </c>
       <c r="U43" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X43" t="n">
-        <v>4.05</v>
+        <v>5.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="O45" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="P45" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.54</v>
+        <v>2.8</v>
       </c>
       <c r="R45" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S45" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="T45" t="n">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="U45" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W45" t="n">
         <v>1.25</v>
       </c>
       <c r="X45" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,37 +6345,37 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.4</v>
+        <v>2.27</v>
       </c>
       <c r="M46" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="O46" t="n">
-        <v>4.32</v>
+        <v>2.8</v>
       </c>
       <c r="P46" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.5</v>
+        <v>3.16</v>
       </c>
       <c r="R46" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S46" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="T46" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="U46" t="n">
         <v>1.41</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
         <v>1.25</v>
@@ -6384,19 +6384,19 @@
         <v>3.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB46" t="n">
         <v>1.33</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD46" t="n">
         <v>2.1</v>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N47" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
-        <v>4.9</v>
+        <v>4.32</v>
       </c>
       <c r="P47" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="R47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W47" t="n">
         <v>1.25</v>
       </c>
-      <c r="S47" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X47" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T48" t="n">
         <v>2.85</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.16</v>
-      </c>
       <c r="U48" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V48" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W48" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="M51" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="O51" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="P51" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y51" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q51" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X51" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z51" t="n">
-        <v>2.63</v>
+        <v>1.53</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.05</v>
+        <v>4.4</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.88</v>
+        <v>1.57</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,77 +7119,77 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="O52" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="P52" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S52" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="T52" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="U52" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="V52" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W52" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X52" t="n">
-        <v>4.65</v>
+        <v>4.95</v>
       </c>
       <c r="Y52" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z52" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AC52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH52" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG52" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2.15</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="M54" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N54" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O54" t="n">
         <v>2.75</v>
       </c>
       <c r="P54" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R54" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S54" t="n">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="T54" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="U54" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="V54" t="n">
         <v>1.02</v>
       </c>
       <c r="W54" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X54" t="n">
-        <v>4.95</v>
+        <v>5.65</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>1.25</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="M55" t="n">
-        <v>3.35</v>
+        <v>3.23</v>
       </c>
       <c r="N55" t="n">
-        <v>4.08</v>
+        <v>3.56</v>
       </c>
       <c r="O55" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="P55" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="R55" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S55" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="T55" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U55" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V55" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X55" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AA55" t="n">
-        <v>4.2</v>
+        <v>3.46</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>1.24</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N56" t="n">
-        <v>3.35</v>
+        <v>4.08</v>
       </c>
       <c r="O56" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="P56" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.38</v>
+        <v>4.75</v>
       </c>
       <c r="R56" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S56" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="T56" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U56" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V56" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W56" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X56" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA56" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="M57" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N57" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O57" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="P57" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.52</v>
+        <v>4.38</v>
       </c>
       <c r="R57" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S57" t="n">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="T57" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U57" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W57" t="n">
         <v>1.33</v>
       </c>
-      <c r="V57" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.31</v>
-      </c>
       <c r="X57" t="n">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AB57" t="n">
         <v>1.25</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P58" t="n">
         <v>1.98</v>
       </c>
-      <c r="M58" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="P58" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q58" t="n">
-        <v>4.75</v>
+        <v>3.52</v>
       </c>
       <c r="R58" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="S58" t="n">
-        <v>2.31</v>
+        <v>2.62</v>
       </c>
       <c r="T58" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="U58" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="V58" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W58" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="X58" t="n">
-        <v>2.35</v>
+        <v>2.92</v>
       </c>
       <c r="Y58" t="n">
         <v>2.3</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA58" t="n">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,61 +8151,61 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="M60" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="O60" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="P60" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.9</v>
+        <v>4.75</v>
       </c>
       <c r="R60" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="S60" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="T60" t="n">
-        <v>2.9</v>
+        <v>3.42</v>
       </c>
       <c r="U60" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="V60" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W60" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="X60" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AA60" t="n">
-        <v>3.46</v>
+        <v>4.65</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
@@ -8218,10 +8218,10 @@
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -8280,31 +8280,31 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="N61" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O61" t="n">
         <v>2.1</v>
       </c>
       <c r="P61" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="R61" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S61" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="T61" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="U61" t="n">
         <v>1.4</v>
@@ -8313,28 +8313,28 @@
         <v>1</v>
       </c>
       <c r="W61" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X61" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA61" t="n">
         <v>3.3</v>
       </c>
-      <c r="Y61" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AB61" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC61" t="n">
         <v>1.95</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH61" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AI61" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="M63" t="n">
         <v>3.1</v>
       </c>
-      <c r="M63" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N63" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="O63" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T63" t="n">
         <v>3.5</v>
       </c>
-      <c r="P63" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T63" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U63" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V63" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="W63" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="X63" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AA63" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC63" t="n">
         <v>1.95</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N64" t="n">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="O64" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R64" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S64" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="T64" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U64" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V64" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="W64" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="X64" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AA64" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC64" t="n">
         <v>1.95</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH64" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AH64" t="n">
-        <v>1.42</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.26</v>
+        <v>1.81</v>
       </c>
       <c r="M68" t="n">
-        <v>2.85</v>
+        <v>3.17</v>
       </c>
       <c r="N68" t="n">
-        <v>3.07</v>
+        <v>3.96</v>
       </c>
       <c r="O68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T68" t="n">
         <v>3.1</v>
       </c>
-      <c r="P68" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R68" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S68" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T68" t="n">
-        <v>3.15</v>
-      </c>
       <c r="U68" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V68" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W68" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="X68" t="n">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
-        <v>4.64</v>
+        <v>4.2</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,77 +9312,77 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="M69" t="n">
-        <v>3.17</v>
+        <v>2.85</v>
       </c>
       <c r="N69" t="n">
-        <v>3.96</v>
+        <v>3.07</v>
       </c>
       <c r="O69" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="P69" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R69" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S69" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X69" t="n">
         <v>2.59</v>
       </c>
-      <c r="T69" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V69" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W69" t="n">
+      <c r="Y69" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
         <v>1.36</v>
       </c>
-      <c r="X69" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD69" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG69" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH69" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45964.85416666666</v>
+        <v>45964.79166666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-11-03.xlsx
+++ b/jogos_2025-11-03.xlsx
@@ -669,34 +669,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="M2" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="P2" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
         <v>2.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.71</v>
+        <v>2.93</v>
       </c>
       <c r="T2" t="n">
-        <v>2.73</v>
+        <v>2.91</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -708,7 +708,7 @@
         <v>3.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Z2" t="n">
         <v>1.87</v>
@@ -717,7 +717,7 @@
         <v>3.14</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC2" t="n">
         <v>1.73</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
         <v>1.25</v>
@@ -966,22 +966,22 @@
         <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Z4" t="n">
         <v>1.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.96</v>
+        <v>4.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.97</v>
+        <v>1.58</v>
       </c>
       <c r="M14" t="n">
-        <v>3.09</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>2.18</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.91</v>
+        <v>4.95</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="X14" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.34</v>
+        <v>2.09</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O16" t="n">
         <v>3.5</v>
       </c>
-      <c r="N16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="O16" t="n">
-        <v>5.45</v>
-      </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.27</v>
+        <v>2.91</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
         <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>5.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="N17" t="n">
-        <v>4.75</v>
+        <v>1.61</v>
       </c>
       <c r="O17" t="n">
-        <v>2.15</v>
+        <v>5.45</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.95</v>
+        <v>2.27</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.82</v>
+        <v>2.64</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.84</v>
+        <v>2.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.94</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v